--- a/Récapitulatif de l'ensemble des données ROD.xlsx
+++ b/Récapitulatif de l'ensemble des données ROD.xlsx
@@ -5,11 +5,12 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="RECAP DATA ROD" sheetId="1" state="visible" r:id="rId3"/>
     <sheet name="Feuille2" sheetId="2" state="visible" r:id="rId4"/>
+    <sheet name="Feuille3" sheetId="3" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">'RECAP DATA ROD'!$B$3:$J$3</definedName>
@@ -24,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1924" uniqueCount="236">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2448" uniqueCount="241">
   <si>
     <t xml:space="preserve">IBIS BUDGET</t>
   </si>
@@ -794,6 +795,75 @@
   <si>
     <t xml:space="preserve">% DE PRODUITS NON-F&amp;B</t>
   </si>
+  <si>
+    <t xml:space="preserve">F_B__RÉCEPTION</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">F_B__</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">SNACKING/COMPTOIR</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">F_B__</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">DISTRIBUTEUR AUTO.</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">NON_F_B__RÉCEPTION</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">NON_F_B__</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">DISTRIBUTEUR AUTO.</t>
+    </r>
+  </si>
 </sst>
 </file>
 
@@ -805,7 +875,7 @@
     <numFmt numFmtId="166" formatCode="0\ %"/>
     <numFmt numFmtId="167" formatCode="0.00\ %"/>
   </numFmts>
-  <fonts count="16">
+  <fonts count="17">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -919,6 +989,12 @@
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <charset val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="11">
@@ -1282,92 +1358,92 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="200">
+  <cellXfs count="202">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1375,23 +1451,23 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1399,27 +1475,27 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1427,27 +1503,27 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1455,27 +1531,27 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="7" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="7" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="7" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="7" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="7" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="7" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="7" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="7" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1483,23 +1559,23 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="7" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="7" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="7" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="7" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="8" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="8" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1507,31 +1583,31 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="13" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="14" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="7" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="7" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="7" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="7" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1539,371 +1615,371 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="7" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="7" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="7" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="14" fillId="7" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="7" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="7" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="7" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="7" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="7" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="7" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="7" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="7" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="7" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="13" fillId="7" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="7" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="7" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="7" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="7" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="7" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="7" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="9" borderId="5" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="9" borderId="5" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="9" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="9" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="7" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="0" fillId="7" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="7" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="7" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="7" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="13" fillId="7" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="7" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="7" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="7" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="7" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="7" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="7" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="7" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="7" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="9" borderId="10" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="9" borderId="10" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="7" borderId="10" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="0" fillId="7" borderId="10" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="7" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="7" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="7" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="7" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="7" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="7" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="7" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="7" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="7" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="7" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="7" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="7" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="7" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="7" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="7" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="7" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="7" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="7" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="7" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="7" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="7" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="7" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="9" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="9" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="8" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="8" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="7" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="7" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="7" borderId="13" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="7" borderId="13" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="7" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="13" fillId="7" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="7" borderId="12" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="0" fillId="7" borderId="12" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="10" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="10" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="10" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="0" fillId="10" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="7" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="13" fillId="7" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="7" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="7" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="9" borderId="3" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="9" borderId="3" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="7" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="7" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="7" borderId="5" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="0" fillId="7" borderId="5" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="7" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="7" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="7" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="7" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="7" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="7" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="8" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="8" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="8" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="8" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="7" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="7" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="8" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="8" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="13" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="13" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="13" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="13" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="13" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="13" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="13" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="13" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="7" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="7" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="7" borderId="13" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="7" borderId="13" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1911,176 +1987,184 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="8" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="8" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="7" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="7" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="6" fillId="7" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="6" fillId="7" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="6" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="6" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="7" borderId="15" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="7" borderId="15" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="7" borderId="16" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="7" borderId="16" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="7" borderId="17" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="7" borderId="17" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="7" borderId="18" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="7" borderId="18" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="7" borderId="19" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="7" borderId="19" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="7" borderId="14" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="7" borderId="14" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="19" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="19" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="16" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="16" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="17" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="17" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="18" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="18" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="7" borderId="18" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="7" borderId="18" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="7" borderId="14" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="7" borderId="14" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="20" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="20" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="18" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="18" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="16" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="16" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="14" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="14" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="7" borderId="15" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="7" borderId="15" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="7" borderId="16" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="7" borderId="16" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="9" borderId="17" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="9" borderId="17" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="9" borderId="18" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="9" borderId="18" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="7" borderId="19" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="7" borderId="19" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="7" borderId="14" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="7" borderId="14" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="19" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="19" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="17" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="17" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="18" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="18" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="19" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="19" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="14" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="14" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="9" borderId="16" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="9" borderId="16" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="7" borderId="17" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="7" borderId="17" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="7" borderId="18" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="7" borderId="18" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="20" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="20" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="6" fillId="7" borderId="17" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="6" fillId="7" borderId="17" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="6" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="6" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="7" borderId="18" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="0" fillId="7" borderId="18" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="9" borderId="19" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="9" borderId="19" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="7" borderId="19" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="0" fillId="7" borderId="19" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="7" borderId="17" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="0" fillId="7" borderId="17" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -2186,37 +2270,37 @@
         <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="0e2841"/>
+        <a:srgbClr val="0E2841"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="e8e8e8"/>
+        <a:srgbClr val="E8E8E8"/>
       </a:lt2>
       <a:accent1>
         <a:srgbClr val="156082"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="e97132"/>
+        <a:srgbClr val="E97132"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="196b24"/>
+        <a:srgbClr val="196B24"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="0f9ed5"/>
+        <a:srgbClr val="0F9ED5"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="a02b93"/>
+        <a:srgbClr val="A02B93"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="4ea72e"/>
+        <a:srgbClr val="4EA72E"/>
       </a:accent6>
       <a:hlink>
         <a:srgbClr val="467886"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="96607d"/>
+        <a:srgbClr val="96607D"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
@@ -2358,7 +2442,7 @@
   <dimension ref="B1:Q137"/>
   <sheetFormatPr defaultColWidth="11.57421875" defaultRowHeight="14.25" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="1.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="1.3"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="2" width="19.28"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="2" width="25.43"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="2" width="32.29"/>
@@ -3002,7 +3086,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B16" s="45"/>
       <c r="C16" s="46"/>
       <c r="D16" s="53" t="s">
@@ -8104,12 +8188,12 @@
   <dimension ref="A1:EA8"/>
   <sheetFormatPr defaultColWidth="10.16015625" defaultRowHeight="13.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="8.04"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="36.54"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="162" width="8.04"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="162" width="36.54"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+      <c r="A1" s="162" t="s">
         <v>22</v>
       </c>
       <c r="B1" s="26" t="s">
@@ -8124,10 +8208,10 @@
       <c r="E1" s="20" t="s">
         <v>71</v>
       </c>
-      <c r="F1" s="162" t="s">
+      <c r="F1" s="163" t="s">
         <v>73</v>
       </c>
-      <c r="G1" s="163" t="s">
+      <c r="G1" s="164" t="s">
         <v>76</v>
       </c>
       <c r="H1" s="53" t="s">
@@ -8151,10 +8235,10 @@
       <c r="N1" s="53" t="s">
         <v>103</v>
       </c>
-      <c r="O1" s="164" t="s">
+      <c r="O1" s="165" t="s">
         <v>104</v>
       </c>
-      <c r="P1" s="165" t="s">
+      <c r="P1" s="166" t="s">
         <v>108</v>
       </c>
       <c r="Q1" s="53" t="s">
@@ -8175,10 +8259,10 @@
       <c r="V1" s="78" t="s">
         <v>118</v>
       </c>
-      <c r="W1" s="166" t="s">
+      <c r="W1" s="167" t="s">
         <v>121</v>
       </c>
-      <c r="X1" s="167" t="s">
+      <c r="X1" s="168" t="s">
         <v>123</v>
       </c>
       <c r="Y1" s="78" t="s">
@@ -8199,10 +8283,10 @@
       <c r="AD1" s="78" t="s">
         <v>126</v>
       </c>
-      <c r="AE1" s="168" t="s">
+      <c r="AE1" s="169" t="s">
         <v>127</v>
       </c>
-      <c r="AF1" s="169" t="s">
+      <c r="AF1" s="170" t="s">
         <v>131</v>
       </c>
       <c r="AG1" s="108" t="s">
@@ -8229,10 +8313,10 @@
       <c r="AN1" s="20" t="s">
         <v>141</v>
       </c>
-      <c r="AO1" s="170" t="s">
+      <c r="AO1" s="171" t="s">
         <v>142</v>
       </c>
-      <c r="AP1" s="171" t="s">
+      <c r="AP1" s="172" t="s">
         <v>144</v>
       </c>
       <c r="AQ1" s="20" t="s">
@@ -8241,10 +8325,10 @@
       <c r="AR1" s="20" t="s">
         <v>146</v>
       </c>
-      <c r="AS1" s="172" t="s">
+      <c r="AS1" s="173" t="s">
         <v>147</v>
       </c>
-      <c r="AT1" s="169" t="s">
+      <c r="AT1" s="170" t="s">
         <v>149</v>
       </c>
       <c r="AU1" s="20" t="s">
@@ -8259,10 +8343,10 @@
       <c r="AX1" s="20" t="s">
         <v>154</v>
       </c>
-      <c r="AY1" s="162" t="s">
+      <c r="AY1" s="163" t="s">
         <v>155</v>
       </c>
-      <c r="AZ1" s="167" t="s">
+      <c r="AZ1" s="168" t="s">
         <v>158</v>
       </c>
       <c r="BA1" s="53" t="s">
@@ -8280,25 +8364,25 @@
       <c r="BE1" s="78" t="s">
         <v>164</v>
       </c>
-      <c r="BF1" s="164" t="s">
+      <c r="BF1" s="165" t="s">
         <v>165</v>
       </c>
-      <c r="BG1" s="165" t="s">
+      <c r="BG1" s="166" t="s">
         <v>167</v>
       </c>
       <c r="BH1" s="53" t="s">
         <v>168</v>
       </c>
-      <c r="BI1" s="173" t="s">
+      <c r="BI1" s="174" t="s">
         <v>169</v>
       </c>
-      <c r="BJ1" s="165" t="s">
+      <c r="BJ1" s="166" t="s">
         <v>171</v>
       </c>
-      <c r="BK1" s="173" t="s">
+      <c r="BK1" s="174" t="s">
         <v>172</v>
       </c>
-      <c r="BL1" s="165" t="s">
+      <c r="BL1" s="166" t="s">
         <v>174</v>
       </c>
       <c r="BM1" s="53" t="s">
@@ -8316,10 +8400,10 @@
       <c r="BQ1" s="53" t="s">
         <v>180</v>
       </c>
-      <c r="BR1" s="173" t="s">
+      <c r="BR1" s="174" t="s">
         <v>181</v>
       </c>
-      <c r="BS1" s="167" t="s">
+      <c r="BS1" s="168" t="s">
         <v>183</v>
       </c>
       <c r="BT1" s="53" t="s">
@@ -8337,13 +8421,13 @@
       <c r="BX1" s="53" t="s">
         <v>188</v>
       </c>
-      <c r="BY1" s="174" t="s">
+      <c r="BY1" s="175" t="s">
         <v>189</v>
       </c>
-      <c r="BZ1" s="175" t="s">
+      <c r="BZ1" s="176" t="s">
         <v>192</v>
       </c>
-      <c r="CA1" s="171" t="s">
+      <c r="CA1" s="172" t="s">
         <v>195</v>
       </c>
       <c r="CB1" s="20" t="s">
@@ -8370,10 +8454,10 @@
       <c r="CI1" s="108" t="s">
         <v>206</v>
       </c>
-      <c r="CJ1" s="176" t="s">
+      <c r="CJ1" s="177" t="s">
         <v>207</v>
       </c>
-      <c r="CK1" s="171" t="s">
+      <c r="CK1" s="172" t="s">
         <v>209</v>
       </c>
       <c r="CL1" s="20" t="s">
@@ -8397,19 +8481,19 @@
       <c r="CR1" s="108" t="s">
         <v>206</v>
       </c>
-      <c r="CS1" s="176" t="s">
+      <c r="CS1" s="177" t="s">
         <v>207</v>
       </c>
-      <c r="CT1" s="171" t="s">
+      <c r="CT1" s="172" t="s">
         <v>211</v>
       </c>
       <c r="CU1" s="108" t="s">
         <v>213</v>
       </c>
-      <c r="CV1" s="176" t="s">
+      <c r="CV1" s="177" t="s">
         <v>215</v>
       </c>
-      <c r="CW1" s="171" t="s">
+      <c r="CW1" s="172" t="s">
         <v>217</v>
       </c>
       <c r="CX1" s="20" t="s">
@@ -8418,19 +8502,19 @@
       <c r="CY1" s="20" t="s">
         <v>219</v>
       </c>
-      <c r="CZ1" s="172" t="s">
+      <c r="CZ1" s="173" t="s">
         <v>220</v>
       </c>
-      <c r="DA1" s="171" t="s">
+      <c r="DA1" s="172" t="s">
         <v>222</v>
       </c>
       <c r="DB1" s="108" t="s">
         <v>213</v>
       </c>
-      <c r="DC1" s="176" t="s">
+      <c r="DC1" s="177" t="s">
         <v>215</v>
       </c>
-      <c r="DD1" s="169" t="s">
+      <c r="DD1" s="170" t="s">
         <v>217</v>
       </c>
       <c r="DE1" s="20" t="s">
@@ -8439,10 +8523,10 @@
       <c r="DF1" s="20" t="s">
         <v>219</v>
       </c>
-      <c r="DG1" s="162" t="s">
+      <c r="DG1" s="163" t="s">
         <v>220</v>
       </c>
-      <c r="DH1" s="167" t="s">
+      <c r="DH1" s="168" t="s">
         <v>78</v>
       </c>
       <c r="DI1" s="53" t="s">
@@ -8451,10 +8535,10 @@
       <c r="DJ1" s="53" t="s">
         <v>229</v>
       </c>
-      <c r="DK1" s="164" t="s">
+      <c r="DK1" s="165" t="s">
         <v>230</v>
       </c>
-      <c r="DL1" s="165" t="s">
+      <c r="DL1" s="166" t="s">
         <v>232</v>
       </c>
       <c r="DM1" s="78" t="s">
@@ -8507,7 +8591,7 @@
       <c r="A2" s="23" t="s">
         <v>29</v>
       </c>
-      <c r="B2" s="177" t="s">
+      <c r="B2" s="178" t="s">
         <v>38</v>
       </c>
       <c r="C2" s="39" t="s">
@@ -8519,10 +8603,10 @@
       <c r="E2" s="23" t="n">
         <v>7.240512</v>
       </c>
-      <c r="F2" s="178" t="n">
+      <c r="F2" s="179" t="n">
         <v>43.689186</v>
       </c>
-      <c r="G2" s="179" t="s">
+      <c r="G2" s="180" t="s">
         <v>0</v>
       </c>
       <c r="H2" s="56" t="n">
@@ -8546,10 +8630,10 @@
       <c r="N2" s="56" t="s">
         <v>81</v>
       </c>
-      <c r="O2" s="180" t="s">
+      <c r="O2" s="181" t="s">
         <v>105</v>
       </c>
-      <c r="P2" s="181"/>
+      <c r="P2" s="182"/>
       <c r="Q2" s="76"/>
       <c r="R2" s="76"/>
       <c r="S2" s="56" t="s">
@@ -8558,16 +8642,16 @@
       <c r="T2" s="76"/>
       <c r="U2" s="76"/>
       <c r="V2" s="76"/>
-      <c r="W2" s="182"/>
-      <c r="X2" s="183"/>
+      <c r="W2" s="183"/>
+      <c r="X2" s="184"/>
       <c r="Y2" s="56"/>
       <c r="Z2" s="56"/>
       <c r="AA2" s="56"/>
       <c r="AB2" s="56"/>
       <c r="AC2" s="56"/>
       <c r="AD2" s="56"/>
-      <c r="AE2" s="184"/>
-      <c r="AF2" s="185" t="n">
+      <c r="AE2" s="185"/>
+      <c r="AF2" s="186" t="n">
         <v>0</v>
       </c>
       <c r="AG2" s="23" t="s">
@@ -8594,10 +8678,10 @@
       <c r="AN2" s="23" t="s">
         <v>81</v>
       </c>
-      <c r="AO2" s="177" t="s">
-        <v>81</v>
-      </c>
-      <c r="AP2" s="186" t="n">
+      <c r="AO2" s="178" t="s">
+        <v>81</v>
+      </c>
+      <c r="AP2" s="187" t="n">
         <v>4</v>
       </c>
       <c r="AQ2" s="23" t="n">
@@ -8606,10 +8690,10 @@
       <c r="AR2" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="AS2" s="187" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT2" s="188" t="s">
+      <c r="AS2" s="188" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT2" s="189" t="s">
         <v>26</v>
       </c>
       <c r="AU2" s="23" t="s">
@@ -8624,10 +8708,10 @@
       <c r="AX2" s="23" t="s">
         <v>81</v>
       </c>
-      <c r="AY2" s="189" t="s">
-        <v>26</v>
-      </c>
-      <c r="AZ2" s="183"/>
+      <c r="AY2" s="190" t="s">
+        <v>26</v>
+      </c>
+      <c r="AZ2" s="184"/>
       <c r="BA2" s="128"/>
       <c r="BB2" s="56" t="s">
         <v>82</v>
@@ -8641,13 +8725,13 @@
       <c r="BE2" s="56" t="s">
         <v>82</v>
       </c>
-      <c r="BF2" s="190"/>
-      <c r="BG2" s="191"/>
+      <c r="BF2" s="191"/>
+      <c r="BG2" s="192"/>
       <c r="BH2" s="56"/>
-      <c r="BI2" s="192"/>
-      <c r="BJ2" s="191"/>
-      <c r="BK2" s="192"/>
-      <c r="BL2" s="191" t="s">
+      <c r="BI2" s="193"/>
+      <c r="BJ2" s="192"/>
+      <c r="BK2" s="193"/>
+      <c r="BL2" s="192" t="s">
         <v>162</v>
       </c>
       <c r="BM2" s="56"/>
@@ -8663,7 +8747,7 @@
       <c r="BQ2" s="56" t="s">
         <v>162</v>
       </c>
-      <c r="BR2" s="192"/>
+      <c r="BR2" s="193"/>
       <c r="BS2" s="56" t="s">
         <v>162</v>
       </c>
@@ -8680,13 +8764,13 @@
       <c r="BX2" s="56" t="s">
         <v>162</v>
       </c>
-      <c r="BY2" s="184" t="s">
-        <v>162</v>
-      </c>
-      <c r="BZ2" s="193" t="s">
-        <v>26</v>
-      </c>
-      <c r="CA2" s="186" t="s">
+      <c r="BY2" s="185" t="s">
+        <v>162</v>
+      </c>
+      <c r="BZ2" s="194" t="s">
+        <v>26</v>
+      </c>
+      <c r="CA2" s="187" t="s">
         <v>26</v>
       </c>
       <c r="CB2" s="128"/>
@@ -8707,8 +8791,8 @@
       </c>
       <c r="CH2" s="128"/>
       <c r="CI2" s="76"/>
-      <c r="CJ2" s="182"/>
-      <c r="CK2" s="186" t="s">
+      <c r="CJ2" s="183"/>
+      <c r="CK2" s="187" t="s">
         <v>23</v>
       </c>
       <c r="CL2" s="128"/>
@@ -8726,36 +8810,36 @@
       </c>
       <c r="CQ2" s="128"/>
       <c r="CR2" s="76"/>
-      <c r="CS2" s="182"/>
-      <c r="CT2" s="186" t="s">
+      <c r="CS2" s="183"/>
+      <c r="CT2" s="187" t="s">
         <v>81</v>
       </c>
       <c r="CU2" s="23" t="n">
         <v>3</v>
       </c>
-      <c r="CV2" s="187" t="n">
+      <c r="CV2" s="188" t="n">
         <v>6</v>
       </c>
-      <c r="CW2" s="186"/>
+      <c r="CW2" s="187"/>
       <c r="CX2" s="23"/>
       <c r="CY2" s="23"/>
-      <c r="CZ2" s="187"/>
-      <c r="DA2" s="186"/>
+      <c r="CZ2" s="188"/>
+      <c r="DA2" s="187"/>
       <c r="DB2" s="23"/>
-      <c r="DC2" s="187"/>
-      <c r="DD2" s="188"/>
+      <c r="DC2" s="188"/>
+      <c r="DD2" s="189"/>
       <c r="DE2" s="23"/>
       <c r="DF2" s="23"/>
-      <c r="DG2" s="189"/>
-      <c r="DH2" s="183" t="n">
+      <c r="DG2" s="190"/>
+      <c r="DH2" s="184" t="n">
         <v>129</v>
       </c>
       <c r="DI2" s="56"/>
       <c r="DJ2" s="56"/>
-      <c r="DK2" s="180" t="n">
+      <c r="DK2" s="181" t="n">
         <v>6</v>
       </c>
-      <c r="DL2" s="194" t="n">
+      <c r="DL2" s="195" t="n">
         <f aca="false">SUM(DM2:DS2)</f>
         <v>0.65</v>
       </c>
@@ -8780,7 +8864,7 @@
       <c r="DS2" s="77" t="n">
         <v>0</v>
       </c>
-      <c r="DT2" s="195" t="n">
+      <c r="DT2" s="196" t="n">
         <f aca="false">SUM(DU2:EA2)</f>
         <v>0.36</v>
       </c>
@@ -8810,7 +8894,7 @@
       <c r="A3" s="23" t="s">
         <v>30</v>
       </c>
-      <c r="B3" s="177" t="s">
+      <c r="B3" s="178" t="s">
         <v>39</v>
       </c>
       <c r="C3" s="39" t="s">
@@ -8822,10 +8906,10 @@
       <c r="E3" s="23" t="n">
         <v>7.754599</v>
       </c>
-      <c r="F3" s="178" t="n">
+      <c r="F3" s="179" t="n">
         <v>48.591522</v>
       </c>
-      <c r="G3" s="179" t="s">
+      <c r="G3" s="180" t="s">
         <v>0</v>
       </c>
       <c r="H3" s="56" t="n">
@@ -8849,10 +8933,10 @@
       <c r="N3" s="56" t="n">
         <v>2025</v>
       </c>
-      <c r="O3" s="180" t="s">
+      <c r="O3" s="181" t="s">
         <v>106</v>
       </c>
-      <c r="P3" s="181"/>
+      <c r="P3" s="182"/>
       <c r="Q3" s="76"/>
       <c r="R3" s="76"/>
       <c r="S3" s="77" t="n">
@@ -8867,18 +8951,18 @@
       <c r="V3" s="56" t="s">
         <v>119</v>
       </c>
-      <c r="W3" s="196" t="n">
+      <c r="W3" s="197" t="n">
         <v>0.8</v>
       </c>
-      <c r="X3" s="183"/>
+      <c r="X3" s="184"/>
       <c r="Y3" s="56"/>
       <c r="Z3" s="56"/>
       <c r="AA3" s="56"/>
       <c r="AB3" s="56"/>
       <c r="AC3" s="56"/>
       <c r="AD3" s="56"/>
-      <c r="AE3" s="184"/>
-      <c r="AF3" s="197" t="n">
+      <c r="AE3" s="185"/>
+      <c r="AF3" s="198" t="n">
         <v>0</v>
       </c>
       <c r="AG3" s="76" t="s">
@@ -8905,10 +8989,10 @@
       <c r="AN3" s="23" t="s">
         <v>23</v>
       </c>
-      <c r="AO3" s="177" t="s">
-        <v>26</v>
-      </c>
-      <c r="AP3" s="186" t="n">
+      <c r="AO3" s="178" t="s">
+        <v>26</v>
+      </c>
+      <c r="AP3" s="187" t="n">
         <v>0</v>
       </c>
       <c r="AQ3" s="23" t="n">
@@ -8917,10 +9001,10 @@
       <c r="AR3" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="AS3" s="187" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT3" s="188" t="s">
+      <c r="AS3" s="188" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT3" s="189" t="s">
         <v>23</v>
       </c>
       <c r="AU3" s="23" t="s">
@@ -8935,10 +9019,10 @@
       <c r="AX3" s="23" t="s">
         <v>23</v>
       </c>
-      <c r="AY3" s="189" t="s">
-        <v>26</v>
-      </c>
-      <c r="AZ3" s="198" t="n">
+      <c r="AY3" s="190" t="s">
+        <v>26</v>
+      </c>
+      <c r="AZ3" s="199" t="n">
         <v>0.6</v>
       </c>
       <c r="BA3" s="129"/>
@@ -8954,19 +9038,19 @@
       <c r="BE3" s="56" t="s">
         <v>82</v>
       </c>
-      <c r="BF3" s="190"/>
-      <c r="BG3" s="199" t="n">
+      <c r="BF3" s="191"/>
+      <c r="BG3" s="200" t="n">
         <v>0.4</v>
       </c>
       <c r="BH3" s="77"/>
-      <c r="BI3" s="196"/>
-      <c r="BJ3" s="199" t="n">
+      <c r="BI3" s="197"/>
+      <c r="BJ3" s="200" t="n">
         <v>0.6</v>
       </c>
-      <c r="BK3" s="196" t="n">
+      <c r="BK3" s="197" t="n">
         <v>0.4</v>
       </c>
-      <c r="BL3" s="191" t="s">
+      <c r="BL3" s="192" t="s">
         <v>162</v>
       </c>
       <c r="BM3" s="56"/>
@@ -8982,7 +9066,7 @@
       <c r="BQ3" s="56" t="s">
         <v>162</v>
       </c>
-      <c r="BR3" s="192"/>
+      <c r="BR3" s="193"/>
       <c r="BS3" s="56" t="s">
         <v>162</v>
       </c>
@@ -8993,11 +9077,11 @@
       <c r="BV3" s="56"/>
       <c r="BW3" s="56"/>
       <c r="BX3" s="56"/>
-      <c r="BY3" s="184"/>
-      <c r="BZ3" s="193" t="s">
-        <v>26</v>
-      </c>
-      <c r="CA3" s="186" t="s">
+      <c r="BY3" s="185"/>
+      <c r="BZ3" s="194" t="s">
+        <v>26</v>
+      </c>
+      <c r="CA3" s="187" t="s">
         <v>26</v>
       </c>
       <c r="CB3" s="128"/>
@@ -9020,8 +9104,8 @@
       <c r="CI3" s="23" t="s">
         <v>162</v>
       </c>
-      <c r="CJ3" s="187"/>
-      <c r="CK3" s="186" t="s">
+      <c r="CJ3" s="188"/>
+      <c r="CK3" s="187" t="s">
         <v>23</v>
       </c>
       <c r="CL3" s="128"/>
@@ -9041,30 +9125,30 @@
       <c r="CR3" s="23" t="s">
         <v>162</v>
       </c>
-      <c r="CS3" s="187"/>
-      <c r="CT3" s="186" t="s">
+      <c r="CS3" s="188"/>
+      <c r="CT3" s="187" t="s">
         <v>81</v>
       </c>
       <c r="CU3" s="23" t="n">
         <v>2</v>
       </c>
-      <c r="CV3" s="187" t="n">
+      <c r="CV3" s="188" t="n">
         <v>2</v>
       </c>
-      <c r="CW3" s="186"/>
+      <c r="CW3" s="187"/>
       <c r="CX3" s="23"/>
       <c r="CY3" s="23"/>
-      <c r="CZ3" s="187"/>
-      <c r="DA3" s="186" t="n">
+      <c r="CZ3" s="188"/>
+      <c r="DA3" s="187" t="n">
         <v>100</v>
       </c>
       <c r="DB3" s="23" t="n">
         <v>3</v>
       </c>
-      <c r="DC3" s="187" t="n">
+      <c r="DC3" s="188" t="n">
         <v>3</v>
       </c>
-      <c r="DD3" s="188" t="s">
+      <c r="DD3" s="189" t="s">
         <v>26</v>
       </c>
       <c r="DE3" s="23" t="s">
@@ -9073,10 +9157,10 @@
       <c r="DF3" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="DG3" s="189" t="s">
-        <v>26</v>
-      </c>
-      <c r="DH3" s="183" t="n">
+      <c r="DG3" s="190" t="s">
+        <v>26</v>
+      </c>
+      <c r="DH3" s="184" t="n">
         <v>97</v>
       </c>
       <c r="DI3" s="56" t="s">
@@ -9085,10 +9169,10 @@
       <c r="DJ3" s="77" t="n">
         <v>0.7</v>
       </c>
-      <c r="DK3" s="180" t="n">
+      <c r="DK3" s="181" t="n">
         <v>2</v>
       </c>
-      <c r="DL3" s="194" t="n">
+      <c r="DL3" s="195" t="n">
         <f aca="false">SUM(DM3:DS3)</f>
         <v>1</v>
       </c>
@@ -9113,7 +9197,7 @@
       <c r="DS3" s="77" t="n">
         <v>0</v>
       </c>
-      <c r="DT3" s="195" t="n">
+      <c r="DT3" s="196" t="n">
         <f aca="false">SUM(DU3:EA3)</f>
         <v>0</v>
       </c>
@@ -9143,7 +9227,7 @@
       <c r="A4" s="23" t="s">
         <v>31</v>
       </c>
-      <c r="B4" s="177" t="s">
+      <c r="B4" s="178" t="s">
         <v>40</v>
       </c>
       <c r="C4" s="39" t="s">
@@ -9155,10 +9239,10 @@
       <c r="E4" s="23" t="n">
         <v>2.519843</v>
       </c>
-      <c r="F4" s="178" t="n">
+      <c r="F4" s="179" t="n">
         <v>49.006733</v>
       </c>
-      <c r="G4" s="179" t="s">
+      <c r="G4" s="180" t="s">
         <v>1</v>
       </c>
       <c r="H4" s="56" t="n">
@@ -9182,10 +9266,10 @@
       <c r="N4" s="56" t="n">
         <v>2015</v>
       </c>
-      <c r="O4" s="180" t="s">
+      <c r="O4" s="181" t="s">
         <v>105</v>
       </c>
-      <c r="P4" s="181"/>
+      <c r="P4" s="182"/>
       <c r="Q4" s="76"/>
       <c r="R4" s="76"/>
       <c r="S4" s="77" t="n">
@@ -9200,18 +9284,18 @@
       <c r="V4" s="56" t="s">
         <v>120</v>
       </c>
-      <c r="W4" s="196" t="n">
+      <c r="W4" s="197" t="n">
         <v>0.98</v>
       </c>
-      <c r="X4" s="183"/>
+      <c r="X4" s="184"/>
       <c r="Y4" s="56"/>
       <c r="Z4" s="56"/>
       <c r="AA4" s="56"/>
       <c r="AB4" s="56"/>
       <c r="AC4" s="56"/>
       <c r="AD4" s="56"/>
-      <c r="AE4" s="184"/>
-      <c r="AF4" s="185" t="n">
+      <c r="AE4" s="185"/>
+      <c r="AF4" s="186" t="n">
         <v>1</v>
       </c>
       <c r="AG4" s="23" t="s">
@@ -9238,10 +9322,10 @@
       <c r="AN4" s="23" t="s">
         <v>23</v>
       </c>
-      <c r="AO4" s="177" t="s">
-        <v>23</v>
-      </c>
-      <c r="AP4" s="186" t="n">
+      <c r="AO4" s="178" t="s">
+        <v>23</v>
+      </c>
+      <c r="AP4" s="187" t="n">
         <v>1</v>
       </c>
       <c r="AQ4" s="23" t="n">
@@ -9250,10 +9334,10 @@
       <c r="AR4" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="AS4" s="187" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT4" s="188" t="s">
+      <c r="AS4" s="188" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT4" s="189" t="s">
         <v>23</v>
       </c>
       <c r="AU4" s="23" t="s">
@@ -9268,10 +9352,10 @@
       <c r="AX4" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="AY4" s="189" t="s">
-        <v>26</v>
-      </c>
-      <c r="AZ4" s="183" t="n">
+      <c r="AY4" s="190" t="s">
+        <v>26</v>
+      </c>
+      <c r="AZ4" s="184" t="n">
         <v>80</v>
       </c>
       <c r="BA4" s="128"/>
@@ -9287,19 +9371,19 @@
       <c r="BE4" s="56" t="s">
         <v>162</v>
       </c>
-      <c r="BF4" s="190"/>
-      <c r="BG4" s="191" t="n">
+      <c r="BF4" s="191"/>
+      <c r="BG4" s="192" t="n">
         <v>20</v>
       </c>
       <c r="BH4" s="56"/>
-      <c r="BI4" s="192"/>
-      <c r="BJ4" s="191" t="n">
+      <c r="BI4" s="193"/>
+      <c r="BJ4" s="192" t="n">
         <v>70</v>
       </c>
-      <c r="BK4" s="192" t="n">
+      <c r="BK4" s="193" t="n">
         <v>30</v>
       </c>
-      <c r="BL4" s="191" t="s">
+      <c r="BL4" s="192" t="s">
         <v>162</v>
       </c>
       <c r="BM4" s="56" t="s">
@@ -9317,7 +9401,7 @@
       <c r="BQ4" s="56" t="s">
         <v>162</v>
       </c>
-      <c r="BR4" s="192"/>
+      <c r="BR4" s="193"/>
       <c r="BS4" s="56" t="s">
         <v>162</v>
       </c>
@@ -9328,13 +9412,13 @@
       <c r="BV4" s="56"/>
       <c r="BW4" s="56"/>
       <c r="BX4" s="56"/>
-      <c r="BY4" s="184" t="s">
-        <v>162</v>
-      </c>
-      <c r="BZ4" s="193" t="s">
-        <v>26</v>
-      </c>
-      <c r="CA4" s="186" t="s">
+      <c r="BY4" s="185" t="s">
+        <v>162</v>
+      </c>
+      <c r="BZ4" s="194" t="s">
+        <v>26</v>
+      </c>
+      <c r="CA4" s="187" t="s">
         <v>26</v>
       </c>
       <c r="CB4" s="128"/>
@@ -9357,8 +9441,8 @@
       <c r="CI4" s="23" t="s">
         <v>162</v>
       </c>
-      <c r="CJ4" s="187"/>
-      <c r="CK4" s="186" t="s">
+      <c r="CJ4" s="188"/>
+      <c r="CK4" s="187" t="s">
         <v>26</v>
       </c>
       <c r="CL4" s="128"/>
@@ -9378,24 +9462,24 @@
       <c r="CR4" s="23" t="s">
         <v>162</v>
       </c>
-      <c r="CS4" s="187"/>
-      <c r="CT4" s="186" t="s">
+      <c r="CS4" s="188"/>
+      <c r="CT4" s="187" t="s">
         <v>81</v>
       </c>
       <c r="CU4" s="23"/>
-      <c r="CV4" s="187"/>
-      <c r="CW4" s="186"/>
+      <c r="CV4" s="188"/>
+      <c r="CW4" s="187"/>
       <c r="CX4" s="23"/>
       <c r="CY4" s="23"/>
-      <c r="CZ4" s="187"/>
-      <c r="DA4" s="186"/>
+      <c r="CZ4" s="188"/>
+      <c r="DA4" s="187"/>
       <c r="DB4" s="23"/>
-      <c r="DC4" s="187"/>
-      <c r="DD4" s="188"/>
+      <c r="DC4" s="188"/>
+      <c r="DD4" s="189"/>
       <c r="DE4" s="23"/>
       <c r="DF4" s="23"/>
-      <c r="DG4" s="189"/>
-      <c r="DH4" s="183" t="n">
+      <c r="DG4" s="190"/>
+      <c r="DH4" s="184" t="n">
         <v>309</v>
       </c>
       <c r="DI4" s="56" t="s">
@@ -9404,10 +9488,10 @@
       <c r="DJ4" s="77" t="n">
         <v>0.95</v>
       </c>
-      <c r="DK4" s="180" t="n">
+      <c r="DK4" s="181" t="n">
         <v>5</v>
       </c>
-      <c r="DL4" s="194" t="n">
+      <c r="DL4" s="195" t="n">
         <f aca="false">SUM(DM4:DS4)</f>
         <v>0</v>
       </c>
@@ -9418,7 +9502,7 @@
       <c r="DQ4" s="77"/>
       <c r="DR4" s="77"/>
       <c r="DS4" s="77"/>
-      <c r="DT4" s="195" t="n">
+      <c r="DT4" s="196" t="n">
         <f aca="false">SUM(DU4:EA4)</f>
         <v>0</v>
       </c>
@@ -9434,7 +9518,7 @@
       <c r="A5" s="23" t="s">
         <v>32</v>
       </c>
-      <c r="B5" s="177" t="s">
+      <c r="B5" s="178" t="s">
         <v>41</v>
       </c>
       <c r="C5" s="39" t="s">
@@ -9446,10 +9530,10 @@
       <c r="E5" s="23" t="n">
         <v>6.6190552711</v>
       </c>
-      <c r="F5" s="178" t="n">
+      <c r="F5" s="179" t="n">
         <v>45.8591651916</v>
       </c>
-      <c r="G5" s="179" t="s">
+      <c r="G5" s="180" t="s">
         <v>2</v>
       </c>
       <c r="H5" s="56" t="n">
@@ -9473,10 +9557,10 @@
       <c r="N5" s="56" t="s">
         <v>81</v>
       </c>
-      <c r="O5" s="180" t="s">
+      <c r="O5" s="181" t="s">
         <v>105</v>
       </c>
-      <c r="P5" s="181"/>
+      <c r="P5" s="182"/>
       <c r="Q5" s="76"/>
       <c r="R5" s="76"/>
       <c r="S5" s="56" t="s">
@@ -9485,16 +9569,16 @@
       <c r="T5" s="76"/>
       <c r="U5" s="76"/>
       <c r="V5" s="76"/>
-      <c r="W5" s="182"/>
-      <c r="X5" s="183"/>
+      <c r="W5" s="183"/>
+      <c r="X5" s="184"/>
       <c r="Y5" s="56"/>
       <c r="Z5" s="56"/>
       <c r="AA5" s="56"/>
       <c r="AB5" s="56"/>
       <c r="AC5" s="56"/>
       <c r="AD5" s="56"/>
-      <c r="AE5" s="184"/>
-      <c r="AF5" s="185" t="n">
+      <c r="AE5" s="185"/>
+      <c r="AF5" s="186" t="n">
         <v>1</v>
       </c>
       <c r="AG5" s="23" t="s">
@@ -9521,10 +9605,10 @@
       <c r="AN5" s="23" t="s">
         <v>81</v>
       </c>
-      <c r="AO5" s="177" t="s">
-        <v>81</v>
-      </c>
-      <c r="AP5" s="186" t="n">
+      <c r="AO5" s="178" t="s">
+        <v>81</v>
+      </c>
+      <c r="AP5" s="187" t="n">
         <v>3</v>
       </c>
       <c r="AQ5" s="23" t="n">
@@ -9533,10 +9617,10 @@
       <c r="AR5" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="AS5" s="187" t="n">
+      <c r="AS5" s="188" t="n">
         <v>1</v>
       </c>
-      <c r="AT5" s="188" t="s">
+      <c r="AT5" s="189" t="s">
         <v>23</v>
       </c>
       <c r="AU5" s="23" t="s">
@@ -9551,10 +9635,10 @@
       <c r="AX5" s="23" t="s">
         <v>23</v>
       </c>
-      <c r="AY5" s="189" t="s">
-        <v>26</v>
-      </c>
-      <c r="AZ5" s="183"/>
+      <c r="AY5" s="190" t="s">
+        <v>26</v>
+      </c>
+      <c r="AZ5" s="184"/>
       <c r="BA5" s="128"/>
       <c r="BB5" s="56" t="s">
         <v>82</v>
@@ -9568,13 +9652,13 @@
       <c r="BE5" s="56" t="s">
         <v>162</v>
       </c>
-      <c r="BF5" s="190"/>
-      <c r="BG5" s="191"/>
+      <c r="BF5" s="191"/>
+      <c r="BG5" s="192"/>
       <c r="BH5" s="56"/>
-      <c r="BI5" s="192"/>
-      <c r="BJ5" s="191"/>
-      <c r="BK5" s="192"/>
-      <c r="BL5" s="191" t="s">
+      <c r="BI5" s="193"/>
+      <c r="BJ5" s="192"/>
+      <c r="BK5" s="193"/>
+      <c r="BL5" s="192" t="s">
         <v>162</v>
       </c>
       <c r="BM5" s="56" t="s">
@@ -9588,10 +9672,10 @@
         <v>162</v>
       </c>
       <c r="BQ5" s="56"/>
-      <c r="BR5" s="192" t="s">
-        <v>162</v>
-      </c>
-      <c r="BS5" s="183" t="s">
+      <c r="BR5" s="193" t="s">
+        <v>162</v>
+      </c>
+      <c r="BS5" s="184" t="s">
         <v>162</v>
       </c>
       <c r="BT5" s="56" t="s">
@@ -9609,13 +9693,13 @@
       <c r="BX5" s="56" t="s">
         <v>162</v>
       </c>
-      <c r="BY5" s="184" t="s">
-        <v>162</v>
-      </c>
-      <c r="BZ5" s="193" t="s">
-        <v>23</v>
-      </c>
-      <c r="CA5" s="186" t="s">
+      <c r="BY5" s="185" t="s">
+        <v>162</v>
+      </c>
+      <c r="BZ5" s="194" t="s">
+        <v>23</v>
+      </c>
+      <c r="CA5" s="187" t="s">
         <v>23</v>
       </c>
       <c r="CB5" s="128"/>
@@ -9638,8 +9722,8 @@
       <c r="CI5" s="23" t="s">
         <v>162</v>
       </c>
-      <c r="CJ5" s="187"/>
-      <c r="CK5" s="186" t="s">
+      <c r="CJ5" s="188"/>
+      <c r="CK5" s="187" t="s">
         <v>26</v>
       </c>
       <c r="CL5" s="128"/>
@@ -9659,32 +9743,32 @@
       <c r="CR5" s="23" t="s">
         <v>162</v>
       </c>
-      <c r="CS5" s="187"/>
-      <c r="CT5" s="186" t="s">
+      <c r="CS5" s="188"/>
+      <c r="CT5" s="187" t="s">
         <v>81</v>
       </c>
       <c r="CU5" s="23"/>
-      <c r="CV5" s="187"/>
-      <c r="CW5" s="186"/>
+      <c r="CV5" s="188"/>
+      <c r="CW5" s="187"/>
       <c r="CX5" s="23"/>
       <c r="CY5" s="23"/>
-      <c r="CZ5" s="187"/>
-      <c r="DA5" s="186"/>
+      <c r="CZ5" s="188"/>
+      <c r="DA5" s="187"/>
       <c r="DB5" s="23"/>
-      <c r="DC5" s="187"/>
-      <c r="DD5" s="188"/>
+      <c r="DC5" s="188"/>
+      <c r="DD5" s="189"/>
       <c r="DE5" s="23"/>
       <c r="DF5" s="23"/>
-      <c r="DG5" s="189"/>
-      <c r="DH5" s="183" t="n">
+      <c r="DG5" s="190"/>
+      <c r="DH5" s="184" t="n">
         <v>572</v>
       </c>
       <c r="DI5" s="56"/>
       <c r="DJ5" s="56"/>
-      <c r="DK5" s="180" t="n">
+      <c r="DK5" s="181" t="n">
         <v>8</v>
       </c>
-      <c r="DL5" s="194" t="n">
+      <c r="DL5" s="195" t="n">
         <f aca="false">SUM(DM5:DS5)</f>
         <v>0.33</v>
       </c>
@@ -9709,7 +9793,7 @@
       <c r="DS5" s="77" t="n">
         <v>0</v>
       </c>
-      <c r="DT5" s="195" t="n">
+      <c r="DT5" s="196" t="n">
         <f aca="false">SUM(DU5:EA5)</f>
         <v>0.68</v>
       </c>
@@ -9735,11 +9819,11 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="B6" s="177" t="s">
+      <c r="B6" s="178" t="s">
         <v>42</v>
       </c>
       <c r="C6" s="39" t="s">
@@ -9751,10 +9835,10 @@
       <c r="E6" s="23" t="n">
         <v>2.282836</v>
       </c>
-      <c r="F6" s="178" t="n">
+      <c r="F6" s="179" t="n">
         <v>48.849778</v>
       </c>
-      <c r="G6" s="179" t="s">
+      <c r="G6" s="180" t="s">
         <v>2</v>
       </c>
       <c r="H6" s="56" t="n">
@@ -9778,10 +9862,10 @@
       <c r="N6" s="56" t="s">
         <v>81</v>
       </c>
-      <c r="O6" s="180" t="s">
+      <c r="O6" s="181" t="s">
         <v>106</v>
       </c>
-      <c r="P6" s="181"/>
+      <c r="P6" s="182"/>
       <c r="Q6" s="76"/>
       <c r="R6" s="76"/>
       <c r="S6" s="56" t="s">
@@ -9790,16 +9874,16 @@
       <c r="T6" s="76"/>
       <c r="U6" s="76"/>
       <c r="V6" s="76"/>
-      <c r="W6" s="182"/>
-      <c r="X6" s="183"/>
+      <c r="W6" s="183"/>
+      <c r="X6" s="184"/>
       <c r="Y6" s="56"/>
       <c r="Z6" s="56"/>
       <c r="AA6" s="56"/>
       <c r="AB6" s="56"/>
       <c r="AC6" s="56"/>
       <c r="AD6" s="56"/>
-      <c r="AE6" s="184"/>
-      <c r="AF6" s="185" t="n">
+      <c r="AE6" s="185"/>
+      <c r="AF6" s="186" t="n">
         <v>1</v>
       </c>
       <c r="AG6" s="23" t="s">
@@ -9826,10 +9910,10 @@
       <c r="AN6" s="23" t="s">
         <v>81</v>
       </c>
-      <c r="AO6" s="177" t="s">
-        <v>81</v>
-      </c>
-      <c r="AP6" s="186" t="n">
+      <c r="AO6" s="178" t="s">
+        <v>81</v>
+      </c>
+      <c r="AP6" s="187" t="n">
         <v>36</v>
       </c>
       <c r="AQ6" s="23" t="n">
@@ -9838,10 +9922,10 @@
       <c r="AR6" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="AS6" s="187" t="n">
+      <c r="AS6" s="188" t="n">
         <v>1</v>
       </c>
-      <c r="AT6" s="188" t="s">
+      <c r="AT6" s="189" t="s">
         <v>23</v>
       </c>
       <c r="AU6" s="23" t="s">
@@ -9856,10 +9940,10 @@
       <c r="AX6" s="23" t="s">
         <v>23</v>
       </c>
-      <c r="AY6" s="189" t="s">
-        <v>26</v>
-      </c>
-      <c r="AZ6" s="183"/>
+      <c r="AY6" s="190" t="s">
+        <v>26</v>
+      </c>
+      <c r="AZ6" s="184"/>
       <c r="BA6" s="128"/>
       <c r="BB6" s="56" t="s">
         <v>82</v>
@@ -9873,13 +9957,13 @@
       <c r="BE6" s="56" t="s">
         <v>162</v>
       </c>
-      <c r="BF6" s="190"/>
-      <c r="BG6" s="191"/>
+      <c r="BF6" s="191"/>
+      <c r="BG6" s="192"/>
       <c r="BH6" s="56"/>
-      <c r="BI6" s="192"/>
-      <c r="BJ6" s="191"/>
-      <c r="BK6" s="192"/>
-      <c r="BL6" s="191" t="s">
+      <c r="BI6" s="193"/>
+      <c r="BJ6" s="192"/>
+      <c r="BK6" s="193"/>
+      <c r="BL6" s="192" t="s">
         <v>162</v>
       </c>
       <c r="BM6" s="56"/>
@@ -9895,10 +9979,10 @@
       <c r="BQ6" s="56" t="s">
         <v>162</v>
       </c>
-      <c r="BR6" s="192" t="s">
-        <v>162</v>
-      </c>
-      <c r="BS6" s="183" t="s">
+      <c r="BR6" s="193" t="s">
+        <v>162</v>
+      </c>
+      <c r="BS6" s="184" t="s">
         <v>162</v>
       </c>
       <c r="BT6" s="56" t="s">
@@ -9916,13 +10000,13 @@
       <c r="BX6" s="56" t="s">
         <v>162</v>
       </c>
-      <c r="BY6" s="184" t="s">
-        <v>162</v>
-      </c>
-      <c r="BZ6" s="193" t="s">
-        <v>26</v>
-      </c>
-      <c r="CA6" s="186" t="s">
+      <c r="BY6" s="185" t="s">
+        <v>162</v>
+      </c>
+      <c r="BZ6" s="194" t="s">
+        <v>26</v>
+      </c>
+      <c r="CA6" s="187" t="s">
         <v>26</v>
       </c>
       <c r="CB6" s="128"/>
@@ -9943,8 +10027,8 @@
       </c>
       <c r="CH6" s="128"/>
       <c r="CI6" s="76"/>
-      <c r="CJ6" s="182"/>
-      <c r="CK6" s="186" t="s">
+      <c r="CJ6" s="183"/>
+      <c r="CK6" s="187" t="s">
         <v>23</v>
       </c>
       <c r="CL6" s="128"/>
@@ -9962,32 +10046,32 @@
       </c>
       <c r="CQ6" s="128"/>
       <c r="CR6" s="76"/>
-      <c r="CS6" s="182"/>
-      <c r="CT6" s="186" t="s">
+      <c r="CS6" s="183"/>
+      <c r="CT6" s="187" t="s">
         <v>81</v>
       </c>
       <c r="CU6" s="23"/>
-      <c r="CV6" s="187"/>
-      <c r="CW6" s="186"/>
+      <c r="CV6" s="188"/>
+      <c r="CW6" s="187"/>
       <c r="CX6" s="23"/>
       <c r="CY6" s="23"/>
-      <c r="CZ6" s="187"/>
-      <c r="DA6" s="186"/>
+      <c r="CZ6" s="188"/>
+      <c r="DA6" s="187"/>
       <c r="DB6" s="23"/>
-      <c r="DC6" s="187"/>
-      <c r="DD6" s="188"/>
+      <c r="DC6" s="188"/>
+      <c r="DD6" s="189"/>
       <c r="DE6" s="23"/>
       <c r="DF6" s="23"/>
-      <c r="DG6" s="189"/>
-      <c r="DH6" s="183" t="n">
+      <c r="DG6" s="190"/>
+      <c r="DH6" s="184" t="n">
         <v>764</v>
       </c>
       <c r="DI6" s="56"/>
       <c r="DJ6" s="56"/>
-      <c r="DK6" s="180" t="n">
+      <c r="DK6" s="181" t="n">
         <v>7</v>
       </c>
-      <c r="DL6" s="194" t="n">
+      <c r="DL6" s="195" t="n">
         <f aca="false">SUM(DM6:DS6)</f>
         <v>0.81</v>
       </c>
@@ -10012,7 +10096,7 @@
       <c r="DS6" s="77" t="n">
         <v>0</v>
       </c>
-      <c r="DT6" s="195" t="n">
+      <c r="DT6" s="196" t="n">
         <f aca="false">SUM(DU6:EA6)</f>
         <v>0.2</v>
       </c>
@@ -10038,11 +10122,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="23" t="s">
         <v>34</v>
       </c>
-      <c r="B7" s="177" t="s">
+      <c r="B7" s="178" t="s">
         <v>43</v>
       </c>
       <c r="C7" s="39" t="s">
@@ -10054,10 +10138,10 @@
       <c r="E7" s="23" t="n">
         <v>2.329923</v>
       </c>
-      <c r="F7" s="178" t="n">
+      <c r="F7" s="179" t="n">
         <v>48.885048</v>
       </c>
-      <c r="G7" s="179" t="s">
+      <c r="G7" s="180" t="s">
         <v>3</v>
       </c>
       <c r="H7" s="56" t="n">
@@ -10081,10 +10165,10 @@
       <c r="N7" s="56" t="s">
         <v>81</v>
       </c>
-      <c r="O7" s="180" t="s">
+      <c r="O7" s="181" t="s">
         <v>106</v>
       </c>
-      <c r="P7" s="181"/>
+      <c r="P7" s="182"/>
       <c r="Q7" s="76"/>
       <c r="R7" s="76"/>
       <c r="S7" s="56" t="s">
@@ -10093,16 +10177,16 @@
       <c r="T7" s="76"/>
       <c r="U7" s="76"/>
       <c r="V7" s="76"/>
-      <c r="W7" s="182"/>
-      <c r="X7" s="183"/>
+      <c r="W7" s="183"/>
+      <c r="X7" s="184"/>
       <c r="Y7" s="56"/>
       <c r="Z7" s="56"/>
       <c r="AA7" s="56"/>
       <c r="AB7" s="56"/>
       <c r="AC7" s="56"/>
       <c r="AD7" s="56"/>
-      <c r="AE7" s="184"/>
-      <c r="AF7" s="185" t="n">
+      <c r="AE7" s="185"/>
+      <c r="AF7" s="186" t="n">
         <v>0</v>
       </c>
       <c r="AG7" s="23" t="s">
@@ -10129,10 +10213,10 @@
       <c r="AN7" s="23" t="s">
         <v>81</v>
       </c>
-      <c r="AO7" s="177" t="s">
-        <v>81</v>
-      </c>
-      <c r="AP7" s="186" t="n">
+      <c r="AO7" s="178" t="s">
+        <v>81</v>
+      </c>
+      <c r="AP7" s="187" t="n">
         <v>1</v>
       </c>
       <c r="AQ7" s="23" t="n">
@@ -10141,10 +10225,10 @@
       <c r="AR7" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="AS7" s="187" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT7" s="188" t="s">
+      <c r="AS7" s="188" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT7" s="189" t="s">
         <v>26</v>
       </c>
       <c r="AU7" s="23" t="s">
@@ -10159,10 +10243,10 @@
       <c r="AX7" s="23" t="s">
         <v>23</v>
       </c>
-      <c r="AY7" s="189" t="s">
-        <v>26</v>
-      </c>
-      <c r="AZ7" s="183"/>
+      <c r="AY7" s="190" t="s">
+        <v>26</v>
+      </c>
+      <c r="AZ7" s="184"/>
       <c r="BA7" s="128"/>
       <c r="BB7" s="56" t="s">
         <v>82</v>
@@ -10176,13 +10260,13 @@
       <c r="BE7" s="56" t="s">
         <v>82</v>
       </c>
-      <c r="BF7" s="190"/>
-      <c r="BG7" s="191"/>
+      <c r="BF7" s="191"/>
+      <c r="BG7" s="192"/>
       <c r="BH7" s="56"/>
-      <c r="BI7" s="192"/>
-      <c r="BJ7" s="191"/>
-      <c r="BK7" s="192"/>
-      <c r="BL7" s="191" t="s">
+      <c r="BI7" s="193"/>
+      <c r="BJ7" s="192"/>
+      <c r="BK7" s="193"/>
+      <c r="BL7" s="192" t="s">
         <v>162</v>
       </c>
       <c r="BM7" s="56" t="s">
@@ -10200,10 +10284,10 @@
       <c r="BQ7" s="56" t="s">
         <v>162</v>
       </c>
-      <c r="BR7" s="192" t="s">
-        <v>162</v>
-      </c>
-      <c r="BS7" s="183" t="s">
+      <c r="BR7" s="193" t="s">
+        <v>162</v>
+      </c>
+      <c r="BS7" s="184" t="s">
         <v>162</v>
       </c>
       <c r="BT7" s="56" t="s">
@@ -10219,13 +10303,13 @@
       <c r="BX7" s="56" t="s">
         <v>162</v>
       </c>
-      <c r="BY7" s="184" t="s">
-        <v>162</v>
-      </c>
-      <c r="BZ7" s="193" t="s">
-        <v>26</v>
-      </c>
-      <c r="CA7" s="186" t="s">
+      <c r="BY7" s="185" t="s">
+        <v>162</v>
+      </c>
+      <c r="BZ7" s="194" t="s">
+        <v>26</v>
+      </c>
+      <c r="CA7" s="187" t="s">
         <v>26</v>
       </c>
       <c r="CB7" s="128"/>
@@ -10248,8 +10332,8 @@
       <c r="CI7" s="23" t="s">
         <v>162</v>
       </c>
-      <c r="CJ7" s="187"/>
-      <c r="CK7" s="186" t="s">
+      <c r="CJ7" s="188"/>
+      <c r="CK7" s="187" t="s">
         <v>23</v>
       </c>
       <c r="CL7" s="128"/>
@@ -10269,32 +10353,32 @@
       <c r="CR7" s="23" t="s">
         <v>162</v>
       </c>
-      <c r="CS7" s="187"/>
-      <c r="CT7" s="186" t="s">
+      <c r="CS7" s="188"/>
+      <c r="CT7" s="187" t="s">
         <v>81</v>
       </c>
       <c r="CU7" s="23"/>
-      <c r="CV7" s="187"/>
-      <c r="CW7" s="186"/>
+      <c r="CV7" s="188"/>
+      <c r="CW7" s="187"/>
       <c r="CX7" s="23"/>
       <c r="CY7" s="23"/>
-      <c r="CZ7" s="187"/>
-      <c r="DA7" s="186"/>
+      <c r="CZ7" s="188"/>
+      <c r="DA7" s="187"/>
       <c r="DB7" s="23"/>
-      <c r="DC7" s="187"/>
-      <c r="DD7" s="188"/>
+      <c r="DC7" s="188"/>
+      <c r="DD7" s="189"/>
       <c r="DE7" s="23"/>
       <c r="DF7" s="23"/>
-      <c r="DG7" s="189"/>
-      <c r="DH7" s="183" t="n">
+      <c r="DG7" s="190"/>
+      <c r="DH7" s="184" t="n">
         <v>305</v>
       </c>
       <c r="DI7" s="56"/>
       <c r="DJ7" s="56"/>
-      <c r="DK7" s="180" t="n">
+      <c r="DK7" s="181" t="n">
         <v>6</v>
       </c>
-      <c r="DL7" s="194" t="n">
+      <c r="DL7" s="195" t="n">
         <f aca="false">SUM(DM7:DS7)</f>
         <v>0.93</v>
       </c>
@@ -10319,7 +10403,7 @@
       <c r="DS7" s="77" t="n">
         <v>0</v>
       </c>
-      <c r="DT7" s="195" t="n">
+      <c r="DT7" s="196" t="n">
         <f aca="false">SUM(DU7:EA7)</f>
         <v>0.06</v>
       </c>
@@ -10349,7 +10433,7 @@
       <c r="A8" s="23" t="s">
         <v>35</v>
       </c>
-      <c r="B8" s="177" t="s">
+      <c r="B8" s="178" t="s">
         <v>44</v>
       </c>
       <c r="C8" s="39" t="s">
@@ -10361,10 +10445,10 @@
       <c r="E8" s="23" t="n">
         <v>2.256274</v>
       </c>
-      <c r="F8" s="178" t="n">
+      <c r="F8" s="179" t="n">
         <v>48.833827</v>
       </c>
-      <c r="G8" s="179" t="s">
+      <c r="G8" s="180" t="s">
         <v>3</v>
       </c>
       <c r="H8" s="56" t="n">
@@ -10388,10 +10472,10 @@
       <c r="N8" s="56" t="s">
         <v>81</v>
       </c>
-      <c r="O8" s="180" t="s">
+      <c r="O8" s="181" t="s">
         <v>106</v>
       </c>
-      <c r="P8" s="181"/>
+      <c r="P8" s="182"/>
       <c r="Q8" s="76"/>
       <c r="R8" s="76"/>
       <c r="S8" s="56" t="s">
@@ -10400,16 +10484,16 @@
       <c r="T8" s="76"/>
       <c r="U8" s="76"/>
       <c r="V8" s="76"/>
-      <c r="W8" s="182"/>
-      <c r="X8" s="183"/>
+      <c r="W8" s="183"/>
+      <c r="X8" s="184"/>
       <c r="Y8" s="56"/>
       <c r="Z8" s="56"/>
       <c r="AA8" s="56"/>
       <c r="AB8" s="56"/>
       <c r="AC8" s="56"/>
       <c r="AD8" s="56"/>
-      <c r="AE8" s="184"/>
-      <c r="AF8" s="185" t="n">
+      <c r="AE8" s="185"/>
+      <c r="AF8" s="186" t="n">
         <v>1</v>
       </c>
       <c r="AG8" s="23" t="s">
@@ -10436,10 +10520,10 @@
       <c r="AN8" s="23" t="s">
         <v>81</v>
       </c>
-      <c r="AO8" s="177" t="s">
-        <v>81</v>
-      </c>
-      <c r="AP8" s="186" t="n">
+      <c r="AO8" s="178" t="s">
+        <v>81</v>
+      </c>
+      <c r="AP8" s="187" t="n">
         <v>13</v>
       </c>
       <c r="AQ8" s="23" t="n">
@@ -10448,10 +10532,10 @@
       <c r="AR8" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="AS8" s="187" t="n">
+      <c r="AS8" s="188" t="n">
         <v>1</v>
       </c>
-      <c r="AT8" s="188" t="s">
+      <c r="AT8" s="189" t="s">
         <v>26</v>
       </c>
       <c r="AU8" s="23" t="s">
@@ -10466,10 +10550,10 @@
       <c r="AX8" s="23" t="s">
         <v>23</v>
       </c>
-      <c r="AY8" s="189" t="s">
-        <v>26</v>
-      </c>
-      <c r="AZ8" s="183"/>
+      <c r="AY8" s="190" t="s">
+        <v>26</v>
+      </c>
+      <c r="AZ8" s="184"/>
       <c r="BA8" s="128"/>
       <c r="BB8" s="56" t="s">
         <v>82</v>
@@ -10483,13 +10567,13 @@
       <c r="BE8" s="56" t="s">
         <v>82</v>
       </c>
-      <c r="BF8" s="190"/>
-      <c r="BG8" s="191"/>
+      <c r="BF8" s="191"/>
+      <c r="BG8" s="192"/>
       <c r="BH8" s="56"/>
-      <c r="BI8" s="192"/>
-      <c r="BJ8" s="191"/>
-      <c r="BK8" s="192"/>
-      <c r="BL8" s="191" t="s">
+      <c r="BI8" s="193"/>
+      <c r="BJ8" s="192"/>
+      <c r="BK8" s="193"/>
+      <c r="BL8" s="192" t="s">
         <v>162</v>
       </c>
       <c r="BM8" s="56" t="s">
@@ -10507,8 +10591,8 @@
       <c r="BQ8" s="56" t="s">
         <v>162</v>
       </c>
-      <c r="BR8" s="192"/>
-      <c r="BS8" s="183" t="s">
+      <c r="BR8" s="193"/>
+      <c r="BS8" s="184" t="s">
         <v>162</v>
       </c>
       <c r="BT8" s="56" t="s">
@@ -10520,11 +10604,11 @@
       <c r="BX8" s="56" t="s">
         <v>162</v>
       </c>
-      <c r="BY8" s="184"/>
-      <c r="BZ8" s="193" t="s">
-        <v>26</v>
-      </c>
-      <c r="CA8" s="186" t="s">
+      <c r="BY8" s="185"/>
+      <c r="BZ8" s="194" t="s">
+        <v>26</v>
+      </c>
+      <c r="CA8" s="187" t="s">
         <v>26</v>
       </c>
       <c r="CB8" s="128"/>
@@ -10547,8 +10631,8 @@
       <c r="CI8" s="23" t="s">
         <v>162</v>
       </c>
-      <c r="CJ8" s="187"/>
-      <c r="CK8" s="186" t="s">
+      <c r="CJ8" s="188"/>
+      <c r="CK8" s="187" t="s">
         <v>23</v>
       </c>
       <c r="CL8" s="128"/>
@@ -10568,32 +10652,32 @@
       <c r="CR8" s="23" t="s">
         <v>162</v>
       </c>
-      <c r="CS8" s="187"/>
-      <c r="CT8" s="186" t="s">
+      <c r="CS8" s="188"/>
+      <c r="CT8" s="187" t="s">
         <v>81</v>
       </c>
       <c r="CU8" s="23"/>
-      <c r="CV8" s="187"/>
-      <c r="CW8" s="186"/>
+      <c r="CV8" s="188"/>
+      <c r="CW8" s="187"/>
       <c r="CX8" s="23"/>
       <c r="CY8" s="23"/>
-      <c r="CZ8" s="187"/>
-      <c r="DA8" s="186"/>
+      <c r="CZ8" s="188"/>
+      <c r="DA8" s="187"/>
       <c r="DB8" s="23"/>
-      <c r="DC8" s="187"/>
-      <c r="DD8" s="188"/>
+      <c r="DC8" s="188"/>
+      <c r="DD8" s="189"/>
       <c r="DE8" s="23"/>
       <c r="DF8" s="23"/>
-      <c r="DG8" s="189"/>
-      <c r="DH8" s="183" t="n">
+      <c r="DG8" s="190"/>
+      <c r="DH8" s="184" t="n">
         <v>191</v>
       </c>
       <c r="DI8" s="56"/>
       <c r="DJ8" s="56"/>
-      <c r="DK8" s="180" t="n">
+      <c r="DK8" s="181" t="n">
         <v>6</v>
       </c>
-      <c r="DL8" s="194" t="n">
+      <c r="DL8" s="195" t="n">
         <f aca="false">SUM(DM8:DS8)</f>
         <v>0.99</v>
       </c>
@@ -10618,7 +10702,7 @@
       <c r="DS8" s="77" t="n">
         <v>0</v>
       </c>
-      <c r="DT8" s="195" t="n">
+      <c r="DT8" s="196" t="n">
         <f aca="false">SUM(DU8:EA8)</f>
         <v>0</v>
       </c>
@@ -10641,6 +10725,2730 @@
         <v>0</v>
       </c>
       <c r="EA8" s="77" t="n">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,Normal"&amp;12&amp;Kffffff&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Normal"&amp;12&amp;KffffffPage &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:EA9"/>
+  <sheetFormatPr defaultColWidth="10.16015625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="35.37"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="13.3"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="23.57"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="E1" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF1" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ1" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP1" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ1" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS1" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT1" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU1" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV1" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW1" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX1" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC1" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD1" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="BE1" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="BL1" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM1" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="BN1" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="BO1" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP1" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ1" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR1" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS1" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT1" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="BU1" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV1" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="BW1" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="BX1" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="BY1" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="CC1" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="CD1" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="CE1" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="CM1" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="CN1" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="DK1" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="DL1" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="DM1" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="DN1" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="DO1" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="DP1" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="DQ1" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="DR1" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="DS1" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="DT1" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="DU1" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="DV1" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="DW1" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="DX1" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="DY1" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="DZ1" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="EA1" s="0" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="16.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="26" t="s">
+        <v>22</v>
+      </c>
+      <c r="B2" s="26" t="s">
+        <v>36</v>
+      </c>
+      <c r="C2" s="38" t="s">
+        <v>59</v>
+      </c>
+      <c r="D2" s="20" t="s">
+        <v>67</v>
+      </c>
+      <c r="E2" s="20" t="s">
+        <v>71</v>
+      </c>
+      <c r="F2" s="163" t="s">
+        <v>73</v>
+      </c>
+      <c r="G2" s="164" t="s">
+        <v>76</v>
+      </c>
+      <c r="H2" s="53" t="s">
+        <v>78</v>
+      </c>
+      <c r="I2" s="53" t="s">
+        <v>79</v>
+      </c>
+      <c r="J2" s="53" t="s">
+        <v>83</v>
+      </c>
+      <c r="K2" s="53" t="s">
+        <v>86</v>
+      </c>
+      <c r="L2" s="53" t="s">
+        <v>93</v>
+      </c>
+      <c r="M2" s="53" t="s">
+        <v>101</v>
+      </c>
+      <c r="N2" s="53" t="s">
+        <v>103</v>
+      </c>
+      <c r="O2" s="165" t="s">
+        <v>104</v>
+      </c>
+      <c r="P2" s="166" t="s">
+        <v>108</v>
+      </c>
+      <c r="Q2" s="53" t="s">
+        <v>110</v>
+      </c>
+      <c r="R2" s="53" t="s">
+        <v>111</v>
+      </c>
+      <c r="S2" s="53" t="s">
+        <v>112</v>
+      </c>
+      <c r="T2" s="78" t="s">
+        <v>114</v>
+      </c>
+      <c r="U2" s="78" t="s">
+        <v>117</v>
+      </c>
+      <c r="V2" s="78" t="s">
+        <v>118</v>
+      </c>
+      <c r="W2" s="167" t="s">
+        <v>121</v>
+      </c>
+      <c r="X2" s="168" t="s">
+        <v>123</v>
+      </c>
+      <c r="Y2" s="78" t="s">
+        <v>125</v>
+      </c>
+      <c r="Z2" s="78" t="s">
+        <v>126</v>
+      </c>
+      <c r="AA2" s="78" t="s">
+        <v>127</v>
+      </c>
+      <c r="AB2" s="53" t="s">
+        <v>128</v>
+      </c>
+      <c r="AC2" s="78" t="s">
+        <v>125</v>
+      </c>
+      <c r="AD2" s="78" t="s">
+        <v>126</v>
+      </c>
+      <c r="AE2" s="169" t="s">
+        <v>127</v>
+      </c>
+      <c r="AF2" s="170" t="s">
+        <v>131</v>
+      </c>
+      <c r="AG2" s="108" t="s">
+        <v>132</v>
+      </c>
+      <c r="AH2" s="108" t="s">
+        <v>135</v>
+      </c>
+      <c r="AI2" s="108" t="s">
+        <v>138</v>
+      </c>
+      <c r="AJ2" s="20" t="s">
+        <v>139</v>
+      </c>
+      <c r="AK2" s="108" t="s">
+        <v>132</v>
+      </c>
+      <c r="AL2" s="108" t="s">
+        <v>135</v>
+      </c>
+      <c r="AM2" s="108" t="s">
+        <v>138</v>
+      </c>
+      <c r="AN2" s="20" t="s">
+        <v>141</v>
+      </c>
+      <c r="AO2" s="171" t="s">
+        <v>142</v>
+      </c>
+      <c r="AP2" s="172" t="s">
+        <v>144</v>
+      </c>
+      <c r="AQ2" s="20" t="s">
+        <v>145</v>
+      </c>
+      <c r="AR2" s="20" t="s">
+        <v>146</v>
+      </c>
+      <c r="AS2" s="173" t="s">
+        <v>147</v>
+      </c>
+      <c r="AT2" s="170" t="s">
+        <v>149</v>
+      </c>
+      <c r="AU2" s="20" t="s">
+        <v>151</v>
+      </c>
+      <c r="AV2" s="20" t="s">
+        <v>152</v>
+      </c>
+      <c r="AW2" s="20" t="s">
+        <v>153</v>
+      </c>
+      <c r="AX2" s="20" t="s">
+        <v>154</v>
+      </c>
+      <c r="AY2" s="163" t="s">
+        <v>155</v>
+      </c>
+      <c r="AZ2" s="168" t="s">
+        <v>158</v>
+      </c>
+      <c r="BA2" s="53" t="s">
+        <v>159</v>
+      </c>
+      <c r="BB2" s="78" t="s">
+        <v>160</v>
+      </c>
+      <c r="BC2" s="78" t="s">
+        <v>161</v>
+      </c>
+      <c r="BD2" s="78" t="s">
+        <v>163</v>
+      </c>
+      <c r="BE2" s="78" t="s">
+        <v>164</v>
+      </c>
+      <c r="BF2" s="165" t="s">
+        <v>165</v>
+      </c>
+      <c r="BG2" s="166" t="s">
+        <v>167</v>
+      </c>
+      <c r="BH2" s="53" t="s">
+        <v>168</v>
+      </c>
+      <c r="BI2" s="174" t="s">
+        <v>169</v>
+      </c>
+      <c r="BJ2" s="166" t="s">
+        <v>171</v>
+      </c>
+      <c r="BK2" s="174" t="s">
+        <v>172</v>
+      </c>
+      <c r="BL2" s="166" t="s">
+        <v>174</v>
+      </c>
+      <c r="BM2" s="53" t="s">
+        <v>176</v>
+      </c>
+      <c r="BN2" s="53" t="s">
+        <v>177</v>
+      </c>
+      <c r="BO2" s="53" t="s">
+        <v>178</v>
+      </c>
+      <c r="BP2" s="53" t="s">
+        <v>179</v>
+      </c>
+      <c r="BQ2" s="53" t="s">
+        <v>180</v>
+      </c>
+      <c r="BR2" s="174" t="s">
+        <v>181</v>
+      </c>
+      <c r="BS2" s="168" t="s">
+        <v>183</v>
+      </c>
+      <c r="BT2" s="53" t="s">
+        <v>184</v>
+      </c>
+      <c r="BU2" s="53" t="s">
+        <v>185</v>
+      </c>
+      <c r="BV2" s="53" t="s">
+        <v>186</v>
+      </c>
+      <c r="BW2" s="53" t="s">
+        <v>187</v>
+      </c>
+      <c r="BX2" s="53" t="s">
+        <v>188</v>
+      </c>
+      <c r="BY2" s="175" t="s">
+        <v>189</v>
+      </c>
+      <c r="BZ2" s="176" t="s">
+        <v>192</v>
+      </c>
+      <c r="CA2" s="172" t="s">
+        <v>195</v>
+      </c>
+      <c r="CB2" s="20" t="s">
+        <v>197</v>
+      </c>
+      <c r="CC2" s="108" t="s">
+        <v>236</v>
+      </c>
+      <c r="CD2" s="201" t="s">
+        <v>237</v>
+      </c>
+      <c r="CE2" s="201" t="s">
+        <v>238</v>
+      </c>
+      <c r="CF2" s="108" t="s">
+        <v>202</v>
+      </c>
+      <c r="CG2" s="108" t="s">
+        <v>203</v>
+      </c>
+      <c r="CH2" s="20" t="s">
+        <v>204</v>
+      </c>
+      <c r="CI2" s="108" t="s">
+        <v>206</v>
+      </c>
+      <c r="CJ2" s="177" t="s">
+        <v>207</v>
+      </c>
+      <c r="CK2" s="172" t="s">
+        <v>209</v>
+      </c>
+      <c r="CL2" s="20" t="s">
+        <v>197</v>
+      </c>
+      <c r="CM2" s="108" t="s">
+        <v>239</v>
+      </c>
+      <c r="CN2" s="201" t="s">
+        <v>240</v>
+      </c>
+      <c r="CO2" s="108" t="s">
+        <v>210</v>
+      </c>
+      <c r="CP2" s="108" t="s">
+        <v>203</v>
+      </c>
+      <c r="CQ2" s="20" t="s">
+        <v>204</v>
+      </c>
+      <c r="CR2" s="108" t="s">
+        <v>206</v>
+      </c>
+      <c r="CS2" s="177" t="s">
+        <v>207</v>
+      </c>
+      <c r="CT2" s="172" t="s">
+        <v>211</v>
+      </c>
+      <c r="CU2" s="108" t="s">
+        <v>213</v>
+      </c>
+      <c r="CV2" s="177" t="s">
+        <v>215</v>
+      </c>
+      <c r="CW2" s="172" t="s">
+        <v>217</v>
+      </c>
+      <c r="CX2" s="20" t="s">
+        <v>218</v>
+      </c>
+      <c r="CY2" s="20" t="s">
+        <v>219</v>
+      </c>
+      <c r="CZ2" s="173" t="s">
+        <v>220</v>
+      </c>
+      <c r="DA2" s="172" t="s">
+        <v>222</v>
+      </c>
+      <c r="DB2" s="108" t="s">
+        <v>213</v>
+      </c>
+      <c r="DC2" s="177" t="s">
+        <v>215</v>
+      </c>
+      <c r="DD2" s="170" t="s">
+        <v>217</v>
+      </c>
+      <c r="DE2" s="20" t="s">
+        <v>218</v>
+      </c>
+      <c r="DF2" s="20" t="s">
+        <v>219</v>
+      </c>
+      <c r="DG2" s="163" t="s">
+        <v>220</v>
+      </c>
+      <c r="DH2" s="168" t="s">
+        <v>78</v>
+      </c>
+      <c r="DI2" s="53" t="s">
+        <v>225</v>
+      </c>
+      <c r="DJ2" s="53" t="s">
+        <v>229</v>
+      </c>
+      <c r="DK2" s="165" t="s">
+        <v>230</v>
+      </c>
+      <c r="DL2" s="166" t="s">
+        <v>232</v>
+      </c>
+      <c r="DM2" s="78" t="s">
+        <v>174</v>
+      </c>
+      <c r="DN2" s="78" t="s">
+        <v>176</v>
+      </c>
+      <c r="DO2" s="78" t="s">
+        <v>177</v>
+      </c>
+      <c r="DP2" s="78" t="s">
+        <v>178</v>
+      </c>
+      <c r="DQ2" s="78" t="s">
+        <v>179</v>
+      </c>
+      <c r="DR2" s="78" t="s">
+        <v>180</v>
+      </c>
+      <c r="DS2" s="78" t="s">
+        <v>181</v>
+      </c>
+      <c r="DT2" s="53" t="s">
+        <v>235</v>
+      </c>
+      <c r="DU2" s="78" t="s">
+        <v>183</v>
+      </c>
+      <c r="DV2" s="78" t="s">
+        <v>184</v>
+      </c>
+      <c r="DW2" s="78" t="s">
+        <v>185</v>
+      </c>
+      <c r="DX2" s="78" t="s">
+        <v>186</v>
+      </c>
+      <c r="DY2" s="78" t="s">
+        <v>187</v>
+      </c>
+      <c r="DZ2" s="78" t="s">
+        <v>188</v>
+      </c>
+      <c r="EA2" s="78" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="23" t="s">
+        <v>29</v>
+      </c>
+      <c r="B3" s="178" t="s">
+        <v>38</v>
+      </c>
+      <c r="C3" s="39" t="s">
+        <v>60</v>
+      </c>
+      <c r="D3" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="E3" s="23" t="n">
+        <v>7.240512</v>
+      </c>
+      <c r="F3" s="179" t="n">
+        <v>43.689186</v>
+      </c>
+      <c r="G3" s="180" t="s">
+        <v>0</v>
+      </c>
+      <c r="H3" s="56" t="n">
+        <v>129</v>
+      </c>
+      <c r="I3" s="56" t="s">
+        <v>81</v>
+      </c>
+      <c r="J3" s="56" t="s">
+        <v>84</v>
+      </c>
+      <c r="K3" s="56" t="s">
+        <v>87</v>
+      </c>
+      <c r="L3" s="56" t="s">
+        <v>94</v>
+      </c>
+      <c r="M3" s="56" t="s">
+        <v>81</v>
+      </c>
+      <c r="N3" s="56" t="s">
+        <v>81</v>
+      </c>
+      <c r="O3" s="181" t="s">
+        <v>105</v>
+      </c>
+      <c r="P3" s="182"/>
+      <c r="Q3" s="76"/>
+      <c r="R3" s="76"/>
+      <c r="S3" s="56" t="s">
+        <v>81</v>
+      </c>
+      <c r="T3" s="76"/>
+      <c r="U3" s="76"/>
+      <c r="V3" s="76"/>
+      <c r="W3" s="183"/>
+      <c r="X3" s="184"/>
+      <c r="Y3" s="56"/>
+      <c r="Z3" s="56"/>
+      <c r="AA3" s="56"/>
+      <c r="AB3" s="56"/>
+      <c r="AC3" s="56"/>
+      <c r="AD3" s="56"/>
+      <c r="AE3" s="185"/>
+      <c r="AF3" s="186" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG3" s="23" t="s">
+        <v>81</v>
+      </c>
+      <c r="AH3" s="23" t="s">
+        <v>81</v>
+      </c>
+      <c r="AI3" s="23" t="s">
+        <v>81</v>
+      </c>
+      <c r="AJ3" s="110" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK3" s="23" t="s">
+        <v>56</v>
+      </c>
+      <c r="AL3" s="23" t="s">
+        <v>56</v>
+      </c>
+      <c r="AM3" s="23" t="s">
+        <v>56</v>
+      </c>
+      <c r="AN3" s="23" t="s">
+        <v>81</v>
+      </c>
+      <c r="AO3" s="178" t="s">
+        <v>81</v>
+      </c>
+      <c r="AP3" s="187" t="n">
+        <v>4</v>
+      </c>
+      <c r="AQ3" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR3" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS3" s="188" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT3" s="189" t="s">
+        <v>26</v>
+      </c>
+      <c r="AU3" s="23" t="s">
+        <v>26</v>
+      </c>
+      <c r="AV3" s="23" t="s">
+        <v>26</v>
+      </c>
+      <c r="AW3" s="23" t="s">
+        <v>26</v>
+      </c>
+      <c r="AX3" s="23" t="s">
+        <v>81</v>
+      </c>
+      <c r="AY3" s="190" t="s">
+        <v>26</v>
+      </c>
+      <c r="AZ3" s="184"/>
+      <c r="BA3" s="128"/>
+      <c r="BB3" s="56" t="s">
+        <v>82</v>
+      </c>
+      <c r="BC3" s="56" t="s">
+        <v>82</v>
+      </c>
+      <c r="BD3" s="56" t="s">
+        <v>162</v>
+      </c>
+      <c r="BE3" s="56" t="s">
+        <v>82</v>
+      </c>
+      <c r="BF3" s="191"/>
+      <c r="BG3" s="192"/>
+      <c r="BH3" s="56"/>
+      <c r="BI3" s="193"/>
+      <c r="BJ3" s="192"/>
+      <c r="BK3" s="193"/>
+      <c r="BL3" s="192" t="s">
+        <v>162</v>
+      </c>
+      <c r="BM3" s="56"/>
+      <c r="BN3" s="56" t="s">
+        <v>162</v>
+      </c>
+      <c r="BO3" s="56" t="s">
+        <v>162</v>
+      </c>
+      <c r="BP3" s="56" t="s">
+        <v>162</v>
+      </c>
+      <c r="BQ3" s="56" t="s">
+        <v>162</v>
+      </c>
+      <c r="BR3" s="193"/>
+      <c r="BS3" s="56" t="s">
+        <v>162</v>
+      </c>
+      <c r="BT3" s="56" t="s">
+        <v>162</v>
+      </c>
+      <c r="BU3" s="56"/>
+      <c r="BV3" s="56" t="s">
+        <v>162</v>
+      </c>
+      <c r="BW3" s="56" t="s">
+        <v>162</v>
+      </c>
+      <c r="BX3" s="56" t="s">
+        <v>162</v>
+      </c>
+      <c r="BY3" s="185" t="s">
+        <v>162</v>
+      </c>
+      <c r="BZ3" s="194" t="s">
+        <v>26</v>
+      </c>
+      <c r="CA3" s="187" t="s">
+        <v>26</v>
+      </c>
+      <c r="CB3" s="128"/>
+      <c r="CC3" s="23" t="s">
+        <v>23</v>
+      </c>
+      <c r="CD3" s="23" t="s">
+        <v>23</v>
+      </c>
+      <c r="CE3" s="23" t="s">
+        <v>26</v>
+      </c>
+      <c r="CF3" s="23" t="s">
+        <v>23</v>
+      </c>
+      <c r="CG3" s="23" t="s">
+        <v>23</v>
+      </c>
+      <c r="CH3" s="128"/>
+      <c r="CI3" s="76"/>
+      <c r="CJ3" s="183"/>
+      <c r="CK3" s="187" t="s">
+        <v>23</v>
+      </c>
+      <c r="CL3" s="128"/>
+      <c r="CM3" s="23" t="s">
+        <v>23</v>
+      </c>
+      <c r="CN3" s="23" t="s">
+        <v>26</v>
+      </c>
+      <c r="CO3" s="23" t="s">
+        <v>23</v>
+      </c>
+      <c r="CP3" s="23" t="s">
+        <v>23</v>
+      </c>
+      <c r="CQ3" s="128"/>
+      <c r="CR3" s="76"/>
+      <c r="CS3" s="183"/>
+      <c r="CT3" s="187" t="s">
+        <v>81</v>
+      </c>
+      <c r="CU3" s="23" t="n">
+        <v>3</v>
+      </c>
+      <c r="CV3" s="188" t="n">
+        <v>6</v>
+      </c>
+      <c r="CW3" s="187"/>
+      <c r="CX3" s="23"/>
+      <c r="CY3" s="23"/>
+      <c r="CZ3" s="188"/>
+      <c r="DA3" s="187"/>
+      <c r="DB3" s="23"/>
+      <c r="DC3" s="188"/>
+      <c r="DD3" s="189"/>
+      <c r="DE3" s="23"/>
+      <c r="DF3" s="23"/>
+      <c r="DG3" s="190"/>
+      <c r="DH3" s="184" t="n">
+        <v>129</v>
+      </c>
+      <c r="DI3" s="56"/>
+      <c r="DJ3" s="56"/>
+      <c r="DK3" s="181" t="n">
+        <v>6</v>
+      </c>
+      <c r="DL3" s="195" t="n">
+        <f aca="false">SUM(DM3:DS3)</f>
+        <v>0.65</v>
+      </c>
+      <c r="DM3" s="77" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="DN3" s="77" t="n">
+        <v>0</v>
+      </c>
+      <c r="DO3" s="77" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="DP3" s="77" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="DQ3" s="77" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="DR3" s="77" t="n">
+        <v>0</v>
+      </c>
+      <c r="DS3" s="77" t="n">
+        <v>0</v>
+      </c>
+      <c r="DT3" s="196" t="n">
+        <f aca="false">SUM(DU3:EA3)</f>
+        <v>0.36</v>
+      </c>
+      <c r="DU3" s="77" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="DV3" s="77" t="n">
+        <v>0</v>
+      </c>
+      <c r="DW3" s="77" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="DX3" s="77" t="n">
+        <v>0</v>
+      </c>
+      <c r="DY3" s="77" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="DZ3" s="77" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="EA3" s="77" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="23" t="s">
+        <v>30</v>
+      </c>
+      <c r="B4" s="178" t="s">
+        <v>39</v>
+      </c>
+      <c r="C4" s="39" t="s">
+        <v>61</v>
+      </c>
+      <c r="D4" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="E4" s="23" t="n">
+        <v>7.754599</v>
+      </c>
+      <c r="F4" s="179" t="n">
+        <v>48.591522</v>
+      </c>
+      <c r="G4" s="180" t="s">
+        <v>0</v>
+      </c>
+      <c r="H4" s="56" t="n">
+        <v>97</v>
+      </c>
+      <c r="I4" s="56" t="n">
+        <v>2020</v>
+      </c>
+      <c r="J4" s="56" t="s">
+        <v>84</v>
+      </c>
+      <c r="K4" s="56" t="s">
+        <v>88</v>
+      </c>
+      <c r="L4" s="56" t="s">
+        <v>95</v>
+      </c>
+      <c r="M4" s="56" t="n">
+        <v>2025</v>
+      </c>
+      <c r="N4" s="56" t="n">
+        <v>2025</v>
+      </c>
+      <c r="O4" s="181" t="s">
+        <v>106</v>
+      </c>
+      <c r="P4" s="182"/>
+      <c r="Q4" s="76"/>
+      <c r="R4" s="76"/>
+      <c r="S4" s="77" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="T4" s="56" t="s">
+        <v>116</v>
+      </c>
+      <c r="U4" s="77" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="V4" s="56" t="s">
+        <v>119</v>
+      </c>
+      <c r="W4" s="197" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="X4" s="184"/>
+      <c r="Y4" s="56"/>
+      <c r="Z4" s="56"/>
+      <c r="AA4" s="56"/>
+      <c r="AB4" s="56"/>
+      <c r="AC4" s="56"/>
+      <c r="AD4" s="56"/>
+      <c r="AE4" s="185"/>
+      <c r="AF4" s="198" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG4" s="76" t="s">
+        <v>133</v>
+      </c>
+      <c r="AH4" s="76" t="s">
+        <v>136</v>
+      </c>
+      <c r="AI4" s="76" t="s">
+        <v>137</v>
+      </c>
+      <c r="AJ4" s="110" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK4" s="23" t="s">
+        <v>56</v>
+      </c>
+      <c r="AL4" s="23" t="s">
+        <v>56</v>
+      </c>
+      <c r="AM4" s="23" t="s">
+        <v>56</v>
+      </c>
+      <c r="AN4" s="23" t="s">
+        <v>23</v>
+      </c>
+      <c r="AO4" s="178" t="s">
+        <v>26</v>
+      </c>
+      <c r="AP4" s="187" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ4" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR4" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS4" s="188" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT4" s="189" t="s">
+        <v>23</v>
+      </c>
+      <c r="AU4" s="23" t="s">
+        <v>23</v>
+      </c>
+      <c r="AV4" s="23" t="s">
+        <v>26</v>
+      </c>
+      <c r="AW4" s="23" t="s">
+        <v>26</v>
+      </c>
+      <c r="AX4" s="23" t="s">
+        <v>23</v>
+      </c>
+      <c r="AY4" s="190" t="s">
+        <v>26</v>
+      </c>
+      <c r="AZ4" s="199" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="BA4" s="129"/>
+      <c r="BB4" s="56" t="s">
+        <v>82</v>
+      </c>
+      <c r="BC4" s="56" t="s">
+        <v>82</v>
+      </c>
+      <c r="BD4" s="56" t="s">
+        <v>162</v>
+      </c>
+      <c r="BE4" s="56" t="s">
+        <v>82</v>
+      </c>
+      <c r="BF4" s="191"/>
+      <c r="BG4" s="200" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="BH4" s="77"/>
+      <c r="BI4" s="197"/>
+      <c r="BJ4" s="200" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="BK4" s="197" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="BL4" s="192" t="s">
+        <v>162</v>
+      </c>
+      <c r="BM4" s="56"/>
+      <c r="BN4" s="56" t="s">
+        <v>162</v>
+      </c>
+      <c r="BO4" s="56" t="s">
+        <v>162</v>
+      </c>
+      <c r="BP4" s="56" t="s">
+        <v>162</v>
+      </c>
+      <c r="BQ4" s="56" t="s">
+        <v>162</v>
+      </c>
+      <c r="BR4" s="193"/>
+      <c r="BS4" s="56" t="s">
+        <v>162</v>
+      </c>
+      <c r="BT4" s="56" t="s">
+        <v>162</v>
+      </c>
+      <c r="BU4" s="56"/>
+      <c r="BV4" s="56"/>
+      <c r="BW4" s="56"/>
+      <c r="BX4" s="56"/>
+      <c r="BY4" s="185"/>
+      <c r="BZ4" s="194" t="s">
+        <v>26</v>
+      </c>
+      <c r="CA4" s="187" t="s">
+        <v>26</v>
+      </c>
+      <c r="CB4" s="128"/>
+      <c r="CC4" s="23" t="s">
+        <v>26</v>
+      </c>
+      <c r="CD4" s="23" t="s">
+        <v>26</v>
+      </c>
+      <c r="CE4" s="23" t="s">
+        <v>26</v>
+      </c>
+      <c r="CF4" s="23" t="s">
+        <v>23</v>
+      </c>
+      <c r="CG4" s="23" t="s">
+        <v>23</v>
+      </c>
+      <c r="CH4" s="128"/>
+      <c r="CI4" s="23" t="s">
+        <v>162</v>
+      </c>
+      <c r="CJ4" s="188"/>
+      <c r="CK4" s="187" t="s">
+        <v>23</v>
+      </c>
+      <c r="CL4" s="128"/>
+      <c r="CM4" s="23" t="s">
+        <v>26</v>
+      </c>
+      <c r="CN4" s="23" t="s">
+        <v>26</v>
+      </c>
+      <c r="CO4" s="23" t="s">
+        <v>23</v>
+      </c>
+      <c r="CP4" s="23" t="s">
+        <v>23</v>
+      </c>
+      <c r="CQ4" s="128"/>
+      <c r="CR4" s="23" t="s">
+        <v>162</v>
+      </c>
+      <c r="CS4" s="188"/>
+      <c r="CT4" s="187" t="s">
+        <v>81</v>
+      </c>
+      <c r="CU4" s="23" t="n">
+        <v>2</v>
+      </c>
+      <c r="CV4" s="188" t="n">
+        <v>2</v>
+      </c>
+      <c r="CW4" s="187"/>
+      <c r="CX4" s="23"/>
+      <c r="CY4" s="23"/>
+      <c r="CZ4" s="188"/>
+      <c r="DA4" s="187" t="n">
+        <v>100</v>
+      </c>
+      <c r="DB4" s="23" t="n">
+        <v>3</v>
+      </c>
+      <c r="DC4" s="188" t="n">
+        <v>3</v>
+      </c>
+      <c r="DD4" s="189" t="s">
+        <v>26</v>
+      </c>
+      <c r="DE4" s="23" t="s">
+        <v>26</v>
+      </c>
+      <c r="DF4" s="23" t="s">
+        <v>26</v>
+      </c>
+      <c r="DG4" s="190" t="s">
+        <v>26</v>
+      </c>
+      <c r="DH4" s="184" t="n">
+        <v>97</v>
+      </c>
+      <c r="DI4" s="56" t="s">
+        <v>227</v>
+      </c>
+      <c r="DJ4" s="77" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="DK4" s="181" t="n">
+        <v>2</v>
+      </c>
+      <c r="DL4" s="195" t="n">
+        <f aca="false">SUM(DM4:DS4)</f>
+        <v>1</v>
+      </c>
+      <c r="DM4" s="77" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="DN4" s="77" t="n">
+        <v>0</v>
+      </c>
+      <c r="DO4" s="77" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="DP4" s="77" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="DQ4" s="77" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="DR4" s="77" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="DS4" s="77" t="n">
+        <v>0</v>
+      </c>
+      <c r="DT4" s="196" t="n">
+        <f aca="false">SUM(DU4:EA4)</f>
+        <v>0</v>
+      </c>
+      <c r="DU4" s="77" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV4" s="77" t="n">
+        <v>0</v>
+      </c>
+      <c r="DW4" s="77" t="n">
+        <v>0</v>
+      </c>
+      <c r="DX4" s="77" t="n">
+        <v>0</v>
+      </c>
+      <c r="DY4" s="77" t="n">
+        <v>0</v>
+      </c>
+      <c r="DZ4" s="77" t="n">
+        <v>0</v>
+      </c>
+      <c r="EA4" s="77" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="23" t="s">
+        <v>31</v>
+      </c>
+      <c r="B5" s="178" t="s">
+        <v>40</v>
+      </c>
+      <c r="C5" s="39" t="s">
+        <v>62</v>
+      </c>
+      <c r="D5" s="23" t="s">
+        <v>68</v>
+      </c>
+      <c r="E5" s="23" t="n">
+        <v>2.519843</v>
+      </c>
+      <c r="F5" s="179" t="n">
+        <v>49.006733</v>
+      </c>
+      <c r="G5" s="180" t="s">
+        <v>1</v>
+      </c>
+      <c r="H5" s="56" t="n">
+        <v>309</v>
+      </c>
+      <c r="I5" s="56" t="n">
+        <v>2015</v>
+      </c>
+      <c r="J5" s="56" t="s">
+        <v>84</v>
+      </c>
+      <c r="K5" s="56" t="s">
+        <v>89</v>
+      </c>
+      <c r="L5" s="56" t="s">
+        <v>96</v>
+      </c>
+      <c r="M5" s="56" t="n">
+        <v>2015</v>
+      </c>
+      <c r="N5" s="56" t="n">
+        <v>2015</v>
+      </c>
+      <c r="O5" s="181" t="s">
+        <v>105</v>
+      </c>
+      <c r="P5" s="182"/>
+      <c r="Q5" s="76"/>
+      <c r="R5" s="76"/>
+      <c r="S5" s="77" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="T5" s="56" t="s">
+        <v>116</v>
+      </c>
+      <c r="U5" s="77" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="V5" s="56" t="s">
+        <v>120</v>
+      </c>
+      <c r="W5" s="197" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="X5" s="184"/>
+      <c r="Y5" s="56"/>
+      <c r="Z5" s="56"/>
+      <c r="AA5" s="56"/>
+      <c r="AB5" s="56"/>
+      <c r="AC5" s="56"/>
+      <c r="AD5" s="56"/>
+      <c r="AE5" s="185"/>
+      <c r="AF5" s="186" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG5" s="23" t="s">
+        <v>134</v>
+      </c>
+      <c r="AH5" s="23" t="s">
+        <v>137</v>
+      </c>
+      <c r="AI5" s="23" t="s">
+        <v>137</v>
+      </c>
+      <c r="AJ5" s="110" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK5" s="23" t="s">
+        <v>140</v>
+      </c>
+      <c r="AL5" s="23" t="s">
+        <v>137</v>
+      </c>
+      <c r="AM5" s="23" t="s">
+        <v>137</v>
+      </c>
+      <c r="AN5" s="23" t="s">
+        <v>23</v>
+      </c>
+      <c r="AO5" s="178" t="s">
+        <v>23</v>
+      </c>
+      <c r="AP5" s="187" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ5" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR5" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS5" s="188" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT5" s="189" t="s">
+        <v>23</v>
+      </c>
+      <c r="AU5" s="23" t="s">
+        <v>26</v>
+      </c>
+      <c r="AV5" s="23" t="s">
+        <v>26</v>
+      </c>
+      <c r="AW5" s="23" t="s">
+        <v>26</v>
+      </c>
+      <c r="AX5" s="23" t="s">
+        <v>26</v>
+      </c>
+      <c r="AY5" s="190" t="s">
+        <v>26</v>
+      </c>
+      <c r="AZ5" s="184" t="n">
+        <v>80</v>
+      </c>
+      <c r="BA5" s="128"/>
+      <c r="BB5" s="56" t="s">
+        <v>82</v>
+      </c>
+      <c r="BC5" s="56" t="s">
+        <v>82</v>
+      </c>
+      <c r="BD5" s="56" t="s">
+        <v>82</v>
+      </c>
+      <c r="BE5" s="56" t="s">
+        <v>162</v>
+      </c>
+      <c r="BF5" s="191"/>
+      <c r="BG5" s="192" t="n">
+        <v>20</v>
+      </c>
+      <c r="BH5" s="56"/>
+      <c r="BI5" s="193"/>
+      <c r="BJ5" s="192" t="n">
+        <v>70</v>
+      </c>
+      <c r="BK5" s="193" t="n">
+        <v>30</v>
+      </c>
+      <c r="BL5" s="192" t="s">
+        <v>162</v>
+      </c>
+      <c r="BM5" s="56" t="s">
+        <v>162</v>
+      </c>
+      <c r="BN5" s="56" t="s">
+        <v>162</v>
+      </c>
+      <c r="BO5" s="56" t="s">
+        <v>162</v>
+      </c>
+      <c r="BP5" s="56" t="s">
+        <v>162</v>
+      </c>
+      <c r="BQ5" s="56" t="s">
+        <v>162</v>
+      </c>
+      <c r="BR5" s="193"/>
+      <c r="BS5" s="56" t="s">
+        <v>162</v>
+      </c>
+      <c r="BT5" s="56" t="s">
+        <v>162</v>
+      </c>
+      <c r="BU5" s="56"/>
+      <c r="BV5" s="56"/>
+      <c r="BW5" s="56"/>
+      <c r="BX5" s="56"/>
+      <c r="BY5" s="185" t="s">
+        <v>162</v>
+      </c>
+      <c r="BZ5" s="194" t="s">
+        <v>26</v>
+      </c>
+      <c r="CA5" s="187" t="s">
+        <v>26</v>
+      </c>
+      <c r="CB5" s="128"/>
+      <c r="CC5" s="23" t="s">
+        <v>26</v>
+      </c>
+      <c r="CD5" s="23" t="s">
+        <v>26</v>
+      </c>
+      <c r="CE5" s="23" t="s">
+        <v>26</v>
+      </c>
+      <c r="CF5" s="23" t="s">
+        <v>23</v>
+      </c>
+      <c r="CG5" s="23" t="s">
+        <v>23</v>
+      </c>
+      <c r="CH5" s="128"/>
+      <c r="CI5" s="23" t="s">
+        <v>162</v>
+      </c>
+      <c r="CJ5" s="188"/>
+      <c r="CK5" s="187" t="s">
+        <v>26</v>
+      </c>
+      <c r="CL5" s="128"/>
+      <c r="CM5" s="23" t="s">
+        <v>26</v>
+      </c>
+      <c r="CN5" s="23" t="s">
+        <v>26</v>
+      </c>
+      <c r="CO5" s="23" t="s">
+        <v>23</v>
+      </c>
+      <c r="CP5" s="23" t="s">
+        <v>23</v>
+      </c>
+      <c r="CQ5" s="128"/>
+      <c r="CR5" s="23" t="s">
+        <v>162</v>
+      </c>
+      <c r="CS5" s="188"/>
+      <c r="CT5" s="187" t="s">
+        <v>81</v>
+      </c>
+      <c r="CU5" s="23"/>
+      <c r="CV5" s="188"/>
+      <c r="CW5" s="187"/>
+      <c r="CX5" s="23"/>
+      <c r="CY5" s="23"/>
+      <c r="CZ5" s="188"/>
+      <c r="DA5" s="187"/>
+      <c r="DB5" s="23"/>
+      <c r="DC5" s="188"/>
+      <c r="DD5" s="189"/>
+      <c r="DE5" s="23"/>
+      <c r="DF5" s="23"/>
+      <c r="DG5" s="190"/>
+      <c r="DH5" s="184" t="n">
+        <v>309</v>
+      </c>
+      <c r="DI5" s="56" t="s">
+        <v>228</v>
+      </c>
+      <c r="DJ5" s="77" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="DK5" s="181" t="n">
+        <v>5</v>
+      </c>
+      <c r="DL5" s="195" t="n">
+        <f aca="false">SUM(DM5:DS5)</f>
+        <v>0</v>
+      </c>
+      <c r="DM5" s="77"/>
+      <c r="DN5" s="77"/>
+      <c r="DO5" s="77"/>
+      <c r="DP5" s="77"/>
+      <c r="DQ5" s="77"/>
+      <c r="DR5" s="77"/>
+      <c r="DS5" s="77"/>
+      <c r="DT5" s="196" t="n">
+        <f aca="false">SUM(DU5:EA5)</f>
+        <v>0</v>
+      </c>
+      <c r="DU5" s="77"/>
+      <c r="DV5" s="77"/>
+      <c r="DW5" s="77"/>
+      <c r="DX5" s="77"/>
+      <c r="DY5" s="77"/>
+      <c r="DZ5" s="77"/>
+      <c r="EA5" s="77"/>
+    </row>
+    <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="23" t="s">
+        <v>32</v>
+      </c>
+      <c r="B6" s="178" t="s">
+        <v>41</v>
+      </c>
+      <c r="C6" s="39" t="s">
+        <v>63</v>
+      </c>
+      <c r="D6" s="23" t="s">
+        <v>16</v>
+      </c>
+      <c r="E6" s="23" t="n">
+        <v>6.6190552711</v>
+      </c>
+      <c r="F6" s="179" t="n">
+        <v>45.8591651916</v>
+      </c>
+      <c r="G6" s="180" t="s">
+        <v>2</v>
+      </c>
+      <c r="H6" s="56" t="n">
+        <v>572</v>
+      </c>
+      <c r="I6" s="56" t="s">
+        <v>81</v>
+      </c>
+      <c r="J6" s="56" t="s">
+        <v>84</v>
+      </c>
+      <c r="K6" s="56" t="s">
+        <v>90</v>
+      </c>
+      <c r="L6" s="56" t="s">
+        <v>97</v>
+      </c>
+      <c r="M6" s="56" t="s">
+        <v>81</v>
+      </c>
+      <c r="N6" s="56" t="s">
+        <v>81</v>
+      </c>
+      <c r="O6" s="181" t="s">
+        <v>105</v>
+      </c>
+      <c r="P6" s="182"/>
+      <c r="Q6" s="76"/>
+      <c r="R6" s="76"/>
+      <c r="S6" s="56" t="s">
+        <v>81</v>
+      </c>
+      <c r="T6" s="76"/>
+      <c r="U6" s="76"/>
+      <c r="V6" s="76"/>
+      <c r="W6" s="183"/>
+      <c r="X6" s="184"/>
+      <c r="Y6" s="56"/>
+      <c r="Z6" s="56"/>
+      <c r="AA6" s="56"/>
+      <c r="AB6" s="56"/>
+      <c r="AC6" s="56"/>
+      <c r="AD6" s="56"/>
+      <c r="AE6" s="185"/>
+      <c r="AF6" s="186" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG6" s="23" t="s">
+        <v>81</v>
+      </c>
+      <c r="AH6" s="23" t="s">
+        <v>81</v>
+      </c>
+      <c r="AI6" s="23" t="s">
+        <v>81</v>
+      </c>
+      <c r="AJ6" s="110" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK6" s="23" t="s">
+        <v>81</v>
+      </c>
+      <c r="AL6" s="23" t="s">
+        <v>81</v>
+      </c>
+      <c r="AM6" s="23" t="s">
+        <v>81</v>
+      </c>
+      <c r="AN6" s="23" t="s">
+        <v>81</v>
+      </c>
+      <c r="AO6" s="178" t="s">
+        <v>81</v>
+      </c>
+      <c r="AP6" s="187" t="n">
+        <v>3</v>
+      </c>
+      <c r="AQ6" s="23" t="n">
+        <v>2</v>
+      </c>
+      <c r="AR6" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS6" s="188" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT6" s="189" t="s">
+        <v>23</v>
+      </c>
+      <c r="AU6" s="23" t="s">
+        <v>23</v>
+      </c>
+      <c r="AV6" s="23" t="s">
+        <v>23</v>
+      </c>
+      <c r="AW6" s="23" t="s">
+        <v>23</v>
+      </c>
+      <c r="AX6" s="23" t="s">
+        <v>23</v>
+      </c>
+      <c r="AY6" s="190" t="s">
+        <v>26</v>
+      </c>
+      <c r="AZ6" s="184"/>
+      <c r="BA6" s="128"/>
+      <c r="BB6" s="56" t="s">
+        <v>82</v>
+      </c>
+      <c r="BC6" s="56" t="s">
+        <v>82</v>
+      </c>
+      <c r="BD6" s="56" t="s">
+        <v>82</v>
+      </c>
+      <c r="BE6" s="56" t="s">
+        <v>162</v>
+      </c>
+      <c r="BF6" s="191"/>
+      <c r="BG6" s="192"/>
+      <c r="BH6" s="56"/>
+      <c r="BI6" s="193"/>
+      <c r="BJ6" s="192"/>
+      <c r="BK6" s="193"/>
+      <c r="BL6" s="192" t="s">
+        <v>162</v>
+      </c>
+      <c r="BM6" s="56" t="s">
+        <v>162</v>
+      </c>
+      <c r="BN6" s="56" t="s">
+        <v>162</v>
+      </c>
+      <c r="BO6" s="56"/>
+      <c r="BP6" s="56" t="s">
+        <v>162</v>
+      </c>
+      <c r="BQ6" s="56"/>
+      <c r="BR6" s="193" t="s">
+        <v>162</v>
+      </c>
+      <c r="BS6" s="184" t="s">
+        <v>162</v>
+      </c>
+      <c r="BT6" s="56" t="s">
+        <v>162</v>
+      </c>
+      <c r="BU6" s="56" t="s">
+        <v>162</v>
+      </c>
+      <c r="BV6" s="56" t="s">
+        <v>162</v>
+      </c>
+      <c r="BW6" s="56" t="s">
+        <v>162</v>
+      </c>
+      <c r="BX6" s="56" t="s">
+        <v>162</v>
+      </c>
+      <c r="BY6" s="185" t="s">
+        <v>162</v>
+      </c>
+      <c r="BZ6" s="194" t="s">
+        <v>23</v>
+      </c>
+      <c r="CA6" s="187" t="s">
+        <v>23</v>
+      </c>
+      <c r="CB6" s="128"/>
+      <c r="CC6" s="23" t="s">
+        <v>26</v>
+      </c>
+      <c r="CD6" s="23" t="s">
+        <v>23</v>
+      </c>
+      <c r="CE6" s="23" t="s">
+        <v>23</v>
+      </c>
+      <c r="CF6" s="23" t="s">
+        <v>23</v>
+      </c>
+      <c r="CG6" s="23" t="s">
+        <v>23</v>
+      </c>
+      <c r="CH6" s="128"/>
+      <c r="CI6" s="23" t="s">
+        <v>162</v>
+      </c>
+      <c r="CJ6" s="188"/>
+      <c r="CK6" s="187" t="s">
+        <v>26</v>
+      </c>
+      <c r="CL6" s="128"/>
+      <c r="CM6" s="23" t="s">
+        <v>26</v>
+      </c>
+      <c r="CN6" s="23" t="s">
+        <v>23</v>
+      </c>
+      <c r="CO6" s="23" t="s">
+        <v>23</v>
+      </c>
+      <c r="CP6" s="23" t="s">
+        <v>23</v>
+      </c>
+      <c r="CQ6" s="128"/>
+      <c r="CR6" s="23" t="s">
+        <v>162</v>
+      </c>
+      <c r="CS6" s="188"/>
+      <c r="CT6" s="187" t="s">
+        <v>81</v>
+      </c>
+      <c r="CU6" s="23"/>
+      <c r="CV6" s="188"/>
+      <c r="CW6" s="187"/>
+      <c r="CX6" s="23"/>
+      <c r="CY6" s="23"/>
+      <c r="CZ6" s="188"/>
+      <c r="DA6" s="187"/>
+      <c r="DB6" s="23"/>
+      <c r="DC6" s="188"/>
+      <c r="DD6" s="189"/>
+      <c r="DE6" s="23"/>
+      <c r="DF6" s="23"/>
+      <c r="DG6" s="190"/>
+      <c r="DH6" s="184" t="n">
+        <v>572</v>
+      </c>
+      <c r="DI6" s="56"/>
+      <c r="DJ6" s="56"/>
+      <c r="DK6" s="181" t="n">
+        <v>8</v>
+      </c>
+      <c r="DL6" s="195" t="n">
+        <f aca="false">SUM(DM6:DS6)</f>
+        <v>0.33</v>
+      </c>
+      <c r="DM6" s="77" t="n">
+        <v>0.07</v>
+      </c>
+      <c r="DN6" s="77" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="DO6" s="77" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="DP6" s="77" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="DQ6" s="77" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="DR6" s="77" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="DS6" s="77" t="n">
+        <v>0</v>
+      </c>
+      <c r="DT6" s="196" t="n">
+        <f aca="false">SUM(DU6:EA6)</f>
+        <v>0.68</v>
+      </c>
+      <c r="DU6" s="77" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="DV6" s="77" t="n">
+        <v>0</v>
+      </c>
+      <c r="DW6" s="77" t="n">
+        <v>0.07</v>
+      </c>
+      <c r="DX6" s="77" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="DY6" s="77" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="DZ6" s="77" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="EA6" s="77" t="n">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="23" t="s">
+        <v>33</v>
+      </c>
+      <c r="B7" s="178" t="s">
+        <v>42</v>
+      </c>
+      <c r="C7" s="39" t="s">
+        <v>64</v>
+      </c>
+      <c r="D7" s="23" t="s">
+        <v>69</v>
+      </c>
+      <c r="E7" s="23" t="n">
+        <v>2.282836</v>
+      </c>
+      <c r="F7" s="179" t="n">
+        <v>48.849778</v>
+      </c>
+      <c r="G7" s="180" t="s">
+        <v>2</v>
+      </c>
+      <c r="H7" s="56" t="n">
+        <v>764</v>
+      </c>
+      <c r="I7" s="56" t="n">
+        <v>1976</v>
+      </c>
+      <c r="J7" s="56" t="s">
+        <v>85</v>
+      </c>
+      <c r="K7" s="56" t="s">
+        <v>91</v>
+      </c>
+      <c r="L7" s="56" t="s">
+        <v>98</v>
+      </c>
+      <c r="M7" s="56" t="s">
+        <v>81</v>
+      </c>
+      <c r="N7" s="56" t="s">
+        <v>81</v>
+      </c>
+      <c r="O7" s="181" t="s">
+        <v>106</v>
+      </c>
+      <c r="P7" s="182"/>
+      <c r="Q7" s="76"/>
+      <c r="R7" s="76"/>
+      <c r="S7" s="56" t="s">
+        <v>81</v>
+      </c>
+      <c r="T7" s="76"/>
+      <c r="U7" s="76"/>
+      <c r="V7" s="76"/>
+      <c r="W7" s="183"/>
+      <c r="X7" s="184"/>
+      <c r="Y7" s="56"/>
+      <c r="Z7" s="56"/>
+      <c r="AA7" s="56"/>
+      <c r="AB7" s="56"/>
+      <c r="AC7" s="56"/>
+      <c r="AD7" s="56"/>
+      <c r="AE7" s="185"/>
+      <c r="AF7" s="186" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG7" s="23" t="s">
+        <v>81</v>
+      </c>
+      <c r="AH7" s="23" t="s">
+        <v>81</v>
+      </c>
+      <c r="AI7" s="23" t="s">
+        <v>81</v>
+      </c>
+      <c r="AJ7" s="110" t="n">
+        <v>3</v>
+      </c>
+      <c r="AK7" s="23" t="s">
+        <v>81</v>
+      </c>
+      <c r="AL7" s="23" t="s">
+        <v>81</v>
+      </c>
+      <c r="AM7" s="23" t="s">
+        <v>81</v>
+      </c>
+      <c r="AN7" s="23" t="s">
+        <v>81</v>
+      </c>
+      <c r="AO7" s="178" t="s">
+        <v>81</v>
+      </c>
+      <c r="AP7" s="187" t="n">
+        <v>36</v>
+      </c>
+      <c r="AQ7" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR7" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS7" s="188" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT7" s="189" t="s">
+        <v>23</v>
+      </c>
+      <c r="AU7" s="23" t="s">
+        <v>23</v>
+      </c>
+      <c r="AV7" s="23" t="s">
+        <v>26</v>
+      </c>
+      <c r="AW7" s="23" t="s">
+        <v>26</v>
+      </c>
+      <c r="AX7" s="23" t="s">
+        <v>23</v>
+      </c>
+      <c r="AY7" s="190" t="s">
+        <v>26</v>
+      </c>
+      <c r="AZ7" s="184"/>
+      <c r="BA7" s="128"/>
+      <c r="BB7" s="56" t="s">
+        <v>82</v>
+      </c>
+      <c r="BC7" s="56" t="s">
+        <v>82</v>
+      </c>
+      <c r="BD7" s="56" t="s">
+        <v>82</v>
+      </c>
+      <c r="BE7" s="56" t="s">
+        <v>162</v>
+      </c>
+      <c r="BF7" s="191"/>
+      <c r="BG7" s="192"/>
+      <c r="BH7" s="56"/>
+      <c r="BI7" s="193"/>
+      <c r="BJ7" s="192"/>
+      <c r="BK7" s="193"/>
+      <c r="BL7" s="192" t="s">
+        <v>162</v>
+      </c>
+      <c r="BM7" s="56"/>
+      <c r="BN7" s="56" t="s">
+        <v>162</v>
+      </c>
+      <c r="BO7" s="56" t="s">
+        <v>162</v>
+      </c>
+      <c r="BP7" s="56" t="s">
+        <v>162</v>
+      </c>
+      <c r="BQ7" s="56" t="s">
+        <v>162</v>
+      </c>
+      <c r="BR7" s="193" t="s">
+        <v>162</v>
+      </c>
+      <c r="BS7" s="184" t="s">
+        <v>162</v>
+      </c>
+      <c r="BT7" s="56" t="s">
+        <v>162</v>
+      </c>
+      <c r="BU7" s="56" t="s">
+        <v>162</v>
+      </c>
+      <c r="BV7" s="56" t="s">
+        <v>162</v>
+      </c>
+      <c r="BW7" s="56" t="s">
+        <v>162</v>
+      </c>
+      <c r="BX7" s="56" t="s">
+        <v>162</v>
+      </c>
+      <c r="BY7" s="185" t="s">
+        <v>162</v>
+      </c>
+      <c r="BZ7" s="194" t="s">
+        <v>26</v>
+      </c>
+      <c r="CA7" s="187" t="s">
+        <v>26</v>
+      </c>
+      <c r="CB7" s="128"/>
+      <c r="CC7" s="23" t="s">
+        <v>23</v>
+      </c>
+      <c r="CD7" s="23" t="s">
+        <v>23</v>
+      </c>
+      <c r="CE7" s="23" t="s">
+        <v>26</v>
+      </c>
+      <c r="CF7" s="23" t="s">
+        <v>23</v>
+      </c>
+      <c r="CG7" s="23" t="s">
+        <v>23</v>
+      </c>
+      <c r="CH7" s="128"/>
+      <c r="CI7" s="76"/>
+      <c r="CJ7" s="183"/>
+      <c r="CK7" s="187" t="s">
+        <v>23</v>
+      </c>
+      <c r="CL7" s="128"/>
+      <c r="CM7" s="23" t="s">
+        <v>23</v>
+      </c>
+      <c r="CN7" s="23" t="s">
+        <v>26</v>
+      </c>
+      <c r="CO7" s="23" t="s">
+        <v>23</v>
+      </c>
+      <c r="CP7" s="23" t="s">
+        <v>23</v>
+      </c>
+      <c r="CQ7" s="128"/>
+      <c r="CR7" s="76"/>
+      <c r="CS7" s="183"/>
+      <c r="CT7" s="187" t="s">
+        <v>81</v>
+      </c>
+      <c r="CU7" s="23"/>
+      <c r="CV7" s="188"/>
+      <c r="CW7" s="187"/>
+      <c r="CX7" s="23"/>
+      <c r="CY7" s="23"/>
+      <c r="CZ7" s="188"/>
+      <c r="DA7" s="187"/>
+      <c r="DB7" s="23"/>
+      <c r="DC7" s="188"/>
+      <c r="DD7" s="189"/>
+      <c r="DE7" s="23"/>
+      <c r="DF7" s="23"/>
+      <c r="DG7" s="190"/>
+      <c r="DH7" s="184" t="n">
+        <v>764</v>
+      </c>
+      <c r="DI7" s="56"/>
+      <c r="DJ7" s="56"/>
+      <c r="DK7" s="181" t="n">
+        <v>7</v>
+      </c>
+      <c r="DL7" s="195" t="n">
+        <f aca="false">SUM(DM7:DS7)</f>
+        <v>0.81</v>
+      </c>
+      <c r="DM7" s="77" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="DN7" s="77" t="n">
+        <v>0</v>
+      </c>
+      <c r="DO7" s="77" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="DP7" s="77" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="DQ7" s="77" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="DR7" s="77" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="DS7" s="77" t="n">
+        <v>0</v>
+      </c>
+      <c r="DT7" s="196" t="n">
+        <f aca="false">SUM(DU7:EA7)</f>
+        <v>0.2</v>
+      </c>
+      <c r="DU7" s="77" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="DV7" s="77" t="n">
+        <v>0</v>
+      </c>
+      <c r="DW7" s="77" t="n">
+        <v>0</v>
+      </c>
+      <c r="DX7" s="77" t="n">
+        <v>0</v>
+      </c>
+      <c r="DY7" s="77" t="n">
+        <v>0</v>
+      </c>
+      <c r="DZ7" s="77" t="n">
+        <v>0.07</v>
+      </c>
+      <c r="EA7" s="77" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="23" t="s">
+        <v>34</v>
+      </c>
+      <c r="B8" s="178" t="s">
+        <v>43</v>
+      </c>
+      <c r="C8" s="39" t="s">
+        <v>65</v>
+      </c>
+      <c r="D8" s="23" t="s">
+        <v>69</v>
+      </c>
+      <c r="E8" s="23" t="n">
+        <v>2.329923</v>
+      </c>
+      <c r="F8" s="179" t="n">
+        <v>48.885048</v>
+      </c>
+      <c r="G8" s="180" t="s">
+        <v>3</v>
+      </c>
+      <c r="H8" s="56" t="n">
+        <v>305</v>
+      </c>
+      <c r="I8" s="56" t="s">
+        <v>81</v>
+      </c>
+      <c r="J8" s="56" t="s">
+        <v>85</v>
+      </c>
+      <c r="K8" s="56" t="s">
+        <v>91</v>
+      </c>
+      <c r="L8" s="56" t="s">
+        <v>99</v>
+      </c>
+      <c r="M8" s="56" t="s">
+        <v>81</v>
+      </c>
+      <c r="N8" s="56" t="s">
+        <v>81</v>
+      </c>
+      <c r="O8" s="181" t="s">
+        <v>106</v>
+      </c>
+      <c r="P8" s="182"/>
+      <c r="Q8" s="76"/>
+      <c r="R8" s="76"/>
+      <c r="S8" s="56" t="s">
+        <v>81</v>
+      </c>
+      <c r="T8" s="76"/>
+      <c r="U8" s="76"/>
+      <c r="V8" s="76"/>
+      <c r="W8" s="183"/>
+      <c r="X8" s="184"/>
+      <c r="Y8" s="56"/>
+      <c r="Z8" s="56"/>
+      <c r="AA8" s="56"/>
+      <c r="AB8" s="56"/>
+      <c r="AC8" s="56"/>
+      <c r="AD8" s="56"/>
+      <c r="AE8" s="185"/>
+      <c r="AF8" s="186" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG8" s="23" t="s">
+        <v>81</v>
+      </c>
+      <c r="AH8" s="23" t="s">
+        <v>81</v>
+      </c>
+      <c r="AI8" s="23" t="s">
+        <v>81</v>
+      </c>
+      <c r="AJ8" s="110" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK8" s="23" t="s">
+        <v>81</v>
+      </c>
+      <c r="AL8" s="23" t="s">
+        <v>81</v>
+      </c>
+      <c r="AM8" s="23" t="s">
+        <v>81</v>
+      </c>
+      <c r="AN8" s="23" t="s">
+        <v>81</v>
+      </c>
+      <c r="AO8" s="178" t="s">
+        <v>81</v>
+      </c>
+      <c r="AP8" s="187" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ8" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR8" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS8" s="188" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT8" s="189" t="s">
+        <v>26</v>
+      </c>
+      <c r="AU8" s="23" t="s">
+        <v>23</v>
+      </c>
+      <c r="AV8" s="23" t="s">
+        <v>23</v>
+      </c>
+      <c r="AW8" s="23" t="s">
+        <v>23</v>
+      </c>
+      <c r="AX8" s="23" t="s">
+        <v>23</v>
+      </c>
+      <c r="AY8" s="190" t="s">
+        <v>26</v>
+      </c>
+      <c r="AZ8" s="184"/>
+      <c r="BA8" s="128"/>
+      <c r="BB8" s="56" t="s">
+        <v>82</v>
+      </c>
+      <c r="BC8" s="56" t="s">
+        <v>162</v>
+      </c>
+      <c r="BD8" s="56" t="s">
+        <v>82</v>
+      </c>
+      <c r="BE8" s="56" t="s">
+        <v>82</v>
+      </c>
+      <c r="BF8" s="191"/>
+      <c r="BG8" s="192"/>
+      <c r="BH8" s="56"/>
+      <c r="BI8" s="193"/>
+      <c r="BJ8" s="192"/>
+      <c r="BK8" s="193"/>
+      <c r="BL8" s="192" t="s">
+        <v>162</v>
+      </c>
+      <c r="BM8" s="56" t="s">
+        <v>162</v>
+      </c>
+      <c r="BN8" s="56" t="s">
+        <v>162</v>
+      </c>
+      <c r="BO8" s="56" t="s">
+        <v>162</v>
+      </c>
+      <c r="BP8" s="56" t="s">
+        <v>162</v>
+      </c>
+      <c r="BQ8" s="56" t="s">
+        <v>162</v>
+      </c>
+      <c r="BR8" s="193" t="s">
+        <v>162</v>
+      </c>
+      <c r="BS8" s="184" t="s">
+        <v>162</v>
+      </c>
+      <c r="BT8" s="56" t="s">
+        <v>162</v>
+      </c>
+      <c r="BU8" s="56" t="s">
+        <v>162</v>
+      </c>
+      <c r="BV8" s="56" t="s">
+        <v>162</v>
+      </c>
+      <c r="BW8" s="56"/>
+      <c r="BX8" s="56" t="s">
+        <v>162</v>
+      </c>
+      <c r="BY8" s="185" t="s">
+        <v>162</v>
+      </c>
+      <c r="BZ8" s="194" t="s">
+        <v>26</v>
+      </c>
+      <c r="CA8" s="187" t="s">
+        <v>26</v>
+      </c>
+      <c r="CB8" s="128"/>
+      <c r="CC8" s="23" t="s">
+        <v>26</v>
+      </c>
+      <c r="CD8" s="23" t="s">
+        <v>23</v>
+      </c>
+      <c r="CE8" s="23" t="s">
+        <v>23</v>
+      </c>
+      <c r="CF8" s="23" t="s">
+        <v>23</v>
+      </c>
+      <c r="CG8" s="23" t="s">
+        <v>23</v>
+      </c>
+      <c r="CH8" s="128"/>
+      <c r="CI8" s="23" t="s">
+        <v>162</v>
+      </c>
+      <c r="CJ8" s="188"/>
+      <c r="CK8" s="187" t="s">
+        <v>23</v>
+      </c>
+      <c r="CL8" s="128"/>
+      <c r="CM8" s="23" t="s">
+        <v>26</v>
+      </c>
+      <c r="CN8" s="23" t="s">
+        <v>23</v>
+      </c>
+      <c r="CO8" s="23" t="s">
+        <v>23</v>
+      </c>
+      <c r="CP8" s="23" t="s">
+        <v>23</v>
+      </c>
+      <c r="CQ8" s="128"/>
+      <c r="CR8" s="23" t="s">
+        <v>162</v>
+      </c>
+      <c r="CS8" s="188"/>
+      <c r="CT8" s="187" t="s">
+        <v>81</v>
+      </c>
+      <c r="CU8" s="23"/>
+      <c r="CV8" s="188"/>
+      <c r="CW8" s="187"/>
+      <c r="CX8" s="23"/>
+      <c r="CY8" s="23"/>
+      <c r="CZ8" s="188"/>
+      <c r="DA8" s="187"/>
+      <c r="DB8" s="23"/>
+      <c r="DC8" s="188"/>
+      <c r="DD8" s="189"/>
+      <c r="DE8" s="23"/>
+      <c r="DF8" s="23"/>
+      <c r="DG8" s="190"/>
+      <c r="DH8" s="184" t="n">
+        <v>305</v>
+      </c>
+      <c r="DI8" s="56"/>
+      <c r="DJ8" s="56"/>
+      <c r="DK8" s="181" t="n">
+        <v>6</v>
+      </c>
+      <c r="DL8" s="195" t="n">
+        <f aca="false">SUM(DM8:DS8)</f>
+        <v>0.93</v>
+      </c>
+      <c r="DM8" s="77" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="DN8" s="77" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="DO8" s="77" t="n">
+        <v>0.07</v>
+      </c>
+      <c r="DP8" s="77" t="n">
+        <v>0</v>
+      </c>
+      <c r="DQ8" s="77" t="n">
+        <v>0.07</v>
+      </c>
+      <c r="DR8" s="77" t="n">
+        <v>0</v>
+      </c>
+      <c r="DS8" s="77" t="n">
+        <v>0</v>
+      </c>
+      <c r="DT8" s="196" t="n">
+        <f aca="false">SUM(DU8:EA8)</f>
+        <v>0.06</v>
+      </c>
+      <c r="DU8" s="77" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="DV8" s="77" t="n">
+        <v>0</v>
+      </c>
+      <c r="DW8" s="77" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="DX8" s="77" t="n">
+        <v>0</v>
+      </c>
+      <c r="DY8" s="77" t="n">
+        <v>0</v>
+      </c>
+      <c r="DZ8" s="77" t="n">
+        <v>0</v>
+      </c>
+      <c r="EA8" s="77" t="n">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="23" t="s">
+        <v>35</v>
+      </c>
+      <c r="B9" s="178" t="s">
+        <v>44</v>
+      </c>
+      <c r="C9" s="39" t="s">
+        <v>66</v>
+      </c>
+      <c r="D9" s="23" t="s">
+        <v>70</v>
+      </c>
+      <c r="E9" s="23" t="n">
+        <v>2.256274</v>
+      </c>
+      <c r="F9" s="179" t="n">
+        <v>48.833827</v>
+      </c>
+      <c r="G9" s="180" t="s">
+        <v>3</v>
+      </c>
+      <c r="H9" s="56" t="n">
+        <v>191</v>
+      </c>
+      <c r="I9" s="56" t="s">
+        <v>81</v>
+      </c>
+      <c r="J9" s="56" t="s">
+        <v>84</v>
+      </c>
+      <c r="K9" s="56" t="s">
+        <v>92</v>
+      </c>
+      <c r="L9" s="56" t="s">
+        <v>100</v>
+      </c>
+      <c r="M9" s="56" t="s">
+        <v>81</v>
+      </c>
+      <c r="N9" s="56" t="s">
+        <v>81</v>
+      </c>
+      <c r="O9" s="181" t="s">
+        <v>106</v>
+      </c>
+      <c r="P9" s="182"/>
+      <c r="Q9" s="76"/>
+      <c r="R9" s="76"/>
+      <c r="S9" s="56" t="s">
+        <v>81</v>
+      </c>
+      <c r="T9" s="76"/>
+      <c r="U9" s="76"/>
+      <c r="V9" s="76"/>
+      <c r="W9" s="183"/>
+      <c r="X9" s="184"/>
+      <c r="Y9" s="56"/>
+      <c r="Z9" s="56"/>
+      <c r="AA9" s="56"/>
+      <c r="AB9" s="56"/>
+      <c r="AC9" s="56"/>
+      <c r="AD9" s="56"/>
+      <c r="AE9" s="185"/>
+      <c r="AF9" s="186" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG9" s="23" t="s">
+        <v>81</v>
+      </c>
+      <c r="AH9" s="23" t="s">
+        <v>81</v>
+      </c>
+      <c r="AI9" s="23" t="s">
+        <v>81</v>
+      </c>
+      <c r="AJ9" s="110" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK9" s="23" t="s">
+        <v>81</v>
+      </c>
+      <c r="AL9" s="23" t="s">
+        <v>81</v>
+      </c>
+      <c r="AM9" s="23" t="s">
+        <v>81</v>
+      </c>
+      <c r="AN9" s="23" t="s">
+        <v>81</v>
+      </c>
+      <c r="AO9" s="178" t="s">
+        <v>81</v>
+      </c>
+      <c r="AP9" s="187" t="n">
+        <v>13</v>
+      </c>
+      <c r="AQ9" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR9" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS9" s="188" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT9" s="189" t="s">
+        <v>26</v>
+      </c>
+      <c r="AU9" s="23" t="s">
+        <v>23</v>
+      </c>
+      <c r="AV9" s="23" t="s">
+        <v>26</v>
+      </c>
+      <c r="AW9" s="23" t="s">
+        <v>23</v>
+      </c>
+      <c r="AX9" s="23" t="s">
+        <v>23</v>
+      </c>
+      <c r="AY9" s="190" t="s">
+        <v>26</v>
+      </c>
+      <c r="AZ9" s="184"/>
+      <c r="BA9" s="128"/>
+      <c r="BB9" s="56" t="s">
+        <v>82</v>
+      </c>
+      <c r="BC9" s="56" t="s">
+        <v>162</v>
+      </c>
+      <c r="BD9" s="56" t="s">
+        <v>82</v>
+      </c>
+      <c r="BE9" s="56" t="s">
+        <v>82</v>
+      </c>
+      <c r="BF9" s="191"/>
+      <c r="BG9" s="192"/>
+      <c r="BH9" s="56"/>
+      <c r="BI9" s="193"/>
+      <c r="BJ9" s="192"/>
+      <c r="BK9" s="193"/>
+      <c r="BL9" s="192" t="s">
+        <v>162</v>
+      </c>
+      <c r="BM9" s="56" t="s">
+        <v>162</v>
+      </c>
+      <c r="BN9" s="56" t="s">
+        <v>162</v>
+      </c>
+      <c r="BO9" s="56" t="s">
+        <v>162</v>
+      </c>
+      <c r="BP9" s="56" t="s">
+        <v>162</v>
+      </c>
+      <c r="BQ9" s="56" t="s">
+        <v>162</v>
+      </c>
+      <c r="BR9" s="193"/>
+      <c r="BS9" s="184" t="s">
+        <v>162</v>
+      </c>
+      <c r="BT9" s="56" t="s">
+        <v>162</v>
+      </c>
+      <c r="BU9" s="56"/>
+      <c r="BV9" s="56"/>
+      <c r="BW9" s="56"/>
+      <c r="BX9" s="56" t="s">
+        <v>162</v>
+      </c>
+      <c r="BY9" s="185"/>
+      <c r="BZ9" s="194" t="s">
+        <v>26</v>
+      </c>
+      <c r="CA9" s="187" t="s">
+        <v>26</v>
+      </c>
+      <c r="CB9" s="128"/>
+      <c r="CC9" s="23" t="s">
+        <v>26</v>
+      </c>
+      <c r="CD9" s="23" t="s">
+        <v>23</v>
+      </c>
+      <c r="CE9" s="23" t="s">
+        <v>23</v>
+      </c>
+      <c r="CF9" s="23" t="s">
+        <v>23</v>
+      </c>
+      <c r="CG9" s="23" t="s">
+        <v>23</v>
+      </c>
+      <c r="CH9" s="128"/>
+      <c r="CI9" s="23" t="s">
+        <v>162</v>
+      </c>
+      <c r="CJ9" s="188"/>
+      <c r="CK9" s="187" t="s">
+        <v>23</v>
+      </c>
+      <c r="CL9" s="128"/>
+      <c r="CM9" s="23" t="s">
+        <v>26</v>
+      </c>
+      <c r="CN9" s="23" t="s">
+        <v>23</v>
+      </c>
+      <c r="CO9" s="23" t="s">
+        <v>23</v>
+      </c>
+      <c r="CP9" s="23" t="s">
+        <v>23</v>
+      </c>
+      <c r="CQ9" s="128"/>
+      <c r="CR9" s="23" t="s">
+        <v>162</v>
+      </c>
+      <c r="CS9" s="188"/>
+      <c r="CT9" s="187" t="s">
+        <v>81</v>
+      </c>
+      <c r="CU9" s="23"/>
+      <c r="CV9" s="188"/>
+      <c r="CW9" s="187"/>
+      <c r="CX9" s="23"/>
+      <c r="CY9" s="23"/>
+      <c r="CZ9" s="188"/>
+      <c r="DA9" s="187"/>
+      <c r="DB9" s="23"/>
+      <c r="DC9" s="188"/>
+      <c r="DD9" s="189"/>
+      <c r="DE9" s="23"/>
+      <c r="DF9" s="23"/>
+      <c r="DG9" s="190"/>
+      <c r="DH9" s="184" t="n">
+        <v>191</v>
+      </c>
+      <c r="DI9" s="56"/>
+      <c r="DJ9" s="56"/>
+      <c r="DK9" s="181" t="n">
+        <v>6</v>
+      </c>
+      <c r="DL9" s="195" t="n">
+        <f aca="false">SUM(DM9:DS9)</f>
+        <v>0.99</v>
+      </c>
+      <c r="DM9" s="77" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="DN9" s="77" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="DO9" s="77" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="DP9" s="77" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="DQ9" s="77" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="DR9" s="77" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="DS9" s="77" t="n">
+        <v>0</v>
+      </c>
+      <c r="DT9" s="196" t="n">
+        <f aca="false">SUM(DU9:EA9)</f>
+        <v>0</v>
+      </c>
+      <c r="DU9" s="77" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV9" s="77" t="n">
+        <v>0</v>
+      </c>
+      <c r="DW9" s="77" t="n">
+        <v>0</v>
+      </c>
+      <c r="DX9" s="77" t="n">
+        <v>0</v>
+      </c>
+      <c r="DY9" s="77" t="n">
+        <v>0</v>
+      </c>
+      <c r="DZ9" s="77" t="n">
+        <v>0</v>
+      </c>
+      <c r="EA9" s="77" t="n">
         <v>0</v>
       </c>
     </row>

--- a/Récapitulatif de l'ensemble des données ROD.xlsx
+++ b/Récapitulatif de l'ensemble des données ROD.xlsx
@@ -799,70 +799,16 @@
     <t xml:space="preserve">F_B__RÉCEPTION</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">F_B__</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">SNACKING/COMPTOIR</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">F_B__</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">DISTRIBUTEUR AUTO.</t>
-    </r>
+    <t xml:space="preserve">F_B__SNACKING/COMPTOIR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">F_B__DISTRIBUTEUR AUTO.</t>
   </si>
   <si>
     <t xml:space="preserve">NON_F_B__RÉCEPTION</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">NON_F_B__</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">DISTRIBUTEUR AUTO.</t>
-    </r>
+    <t xml:space="preserve">NON_F_B__DISTRIBUTEUR AUTO.</t>
   </si>
 </sst>
 </file>
@@ -875,7 +821,7 @@
     <numFmt numFmtId="166" formatCode="0\ %"/>
     <numFmt numFmtId="167" formatCode="0.00\ %"/>
   </numFmts>
-  <fonts count="17">
+  <fonts count="16">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -989,12 +935,6 @@
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <charset val="1"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="11">
@@ -1358,7 +1298,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="202">
+  <cellXfs count="201">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -2161,10 +2101,6 @@
     </xf>
     <xf numFmtId="166" fontId="0" fillId="7" borderId="17" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -10747,176 +10683,140 @@
   <dimension ref="A1:EA9"/>
   <sheetFormatPr defaultColWidth="10.16015625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="35.37"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="13.3"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="23.57"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="162" width="35.37"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="162" width="13.3"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="162" width="23.57"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="n">
+      <c r="A1" s="162" t="n">
         <v>1</v>
       </c>
-      <c r="E1" s="0" t="n">
+      <c r="B1" s="162" t="n">
         <v>1</v>
       </c>
-      <c r="F1" s="0" t="n">
+      <c r="E1" s="162" t="n">
         <v>1</v>
       </c>
-      <c r="G1" s="0" t="n">
+      <c r="F1" s="162" t="n">
         <v>1</v>
       </c>
-      <c r="H1" s="0" t="n">
+      <c r="G1" s="162" t="n">
         <v>1</v>
       </c>
-      <c r="AF1" s="0" t="n">
+      <c r="H1" s="162" t="n">
         <v>1</v>
       </c>
-      <c r="AJ1" s="0" t="n">
+      <c r="I1" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="AP1" s="0" t="n">
+      <c r="M1" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="AQ1" s="0" t="n">
+      <c r="N1" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="AS1" s="0" t="n">
+      <c r="O1" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="AT1" s="0" t="n">
+      <c r="S1" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="AU1" s="0" t="n">
+      <c r="U1" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="AV1" s="0" t="n">
+      <c r="W1" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="AW1" s="0" t="n">
+      <c r="AF1" s="162" t="n">
         <v>1</v>
       </c>
-      <c r="AX1" s="0" t="n">
+      <c r="AJ1" s="162" t="n">
         <v>1</v>
       </c>
-      <c r="BC1" s="0" t="n">
+      <c r="AP1" s="162" t="n">
         <v>1</v>
       </c>
-      <c r="BD1" s="0" t="n">
+      <c r="AQ1" s="162" t="n">
         <v>1</v>
       </c>
-      <c r="BE1" s="0" t="n">
+      <c r="AS1" s="162" t="n">
         <v>1</v>
       </c>
-      <c r="BL1" s="0" t="n">
+      <c r="AT1" s="162" t="n">
         <v>1</v>
       </c>
-      <c r="BM1" s="0" t="n">
+      <c r="AU1" s="162" t="n">
         <v>1</v>
       </c>
-      <c r="BN1" s="0" t="n">
+      <c r="AV1" s="162" t="n">
         <v>1</v>
       </c>
-      <c r="BO1" s="0" t="n">
+      <c r="AW1" s="162" t="n">
         <v>1</v>
       </c>
-      <c r="BP1" s="0" t="n">
+      <c r="AX1" s="162" t="n">
         <v>1</v>
       </c>
-      <c r="BQ1" s="0" t="n">
+      <c r="AZ1" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="BR1" s="0" t="n">
+      <c r="BC1" s="162" t="n">
         <v>1</v>
       </c>
-      <c r="BS1" s="0" t="n">
+      <c r="BD1" s="162" t="n">
         <v>1</v>
       </c>
-      <c r="BT1" s="0" t="n">
+      <c r="BE1" s="162" t="n">
         <v>1</v>
       </c>
-      <c r="BU1" s="0" t="n">
+      <c r="BG1" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="BV1" s="0" t="n">
+      <c r="BJ1" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="BW1" s="0" t="n">
+      <c r="BK1" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="BX1" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="BY1" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="CC1" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="CD1" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="CE1" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="CM1" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="CN1" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="DK1" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="DL1" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="DM1" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="DN1" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="DO1" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="DP1" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="DQ1" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="DR1" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="DS1" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="DT1" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="DU1" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="DV1" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="DW1" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="DX1" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="DY1" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="DZ1" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="EA1" s="0" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="16.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="BL1" s="162"/>
+      <c r="BM1" s="162"/>
+      <c r="BN1" s="162"/>
+      <c r="BO1" s="162"/>
+      <c r="BP1" s="162"/>
+      <c r="BQ1" s="162"/>
+      <c r="BR1" s="162"/>
+      <c r="BS1" s="162"/>
+      <c r="BT1" s="162"/>
+      <c r="BU1" s="162"/>
+      <c r="BV1" s="162"/>
+      <c r="BW1" s="162"/>
+      <c r="BX1" s="162"/>
+      <c r="BY1" s="162"/>
+      <c r="CC1" s="162"/>
+      <c r="CD1" s="162"/>
+      <c r="CE1" s="162"/>
+      <c r="CM1" s="162"/>
+      <c r="CN1" s="162"/>
+      <c r="DK1" s="162"/>
+      <c r="DL1" s="162"/>
+      <c r="DM1" s="162"/>
+      <c r="DN1" s="162"/>
+      <c r="DO1" s="162"/>
+      <c r="DP1" s="162"/>
+      <c r="DQ1" s="162"/>
+      <c r="DR1" s="162"/>
+      <c r="DS1" s="162"/>
+      <c r="DT1" s="162"/>
+      <c r="DU1" s="162"/>
+      <c r="DV1" s="162"/>
+      <c r="DW1" s="162"/>
+      <c r="DX1" s="162"/>
+      <c r="DY1" s="162"/>
+      <c r="DZ1" s="162"/>
+      <c r="EA1" s="162"/>
+    </row>
+    <row r="2" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="26" t="s">
         <v>22</v>
       </c>
@@ -11160,10 +11060,10 @@
       <c r="CC2" s="108" t="s">
         <v>236</v>
       </c>
-      <c r="CD2" s="201" t="s">
+      <c r="CD2" s="108" t="s">
         <v>237</v>
       </c>
-      <c r="CE2" s="201" t="s">
+      <c r="CE2" s="108" t="s">
         <v>238</v>
       </c>
       <c r="CF2" s="108" t="s">
@@ -11190,7 +11090,7 @@
       <c r="CM2" s="108" t="s">
         <v>239</v>
       </c>
-      <c r="CN2" s="201" t="s">
+      <c r="CN2" s="108" t="s">
         <v>240</v>
       </c>
       <c r="CO2" s="108" t="s">
@@ -11746,8 +11646,8 @@
       <c r="AY4" s="190" t="s">
         <v>26</v>
       </c>
-      <c r="AZ4" s="199" t="n">
-        <v>0.6</v>
+      <c r="AZ4" s="184" t="n">
+        <v>60</v>
       </c>
       <c r="BA4" s="129"/>
       <c r="BB4" s="56" t="s">
@@ -11763,16 +11663,16 @@
         <v>82</v>
       </c>
       <c r="BF4" s="191"/>
-      <c r="BG4" s="200" t="n">
-        <v>0.4</v>
+      <c r="BG4" s="192" t="n">
+        <v>40</v>
       </c>
       <c r="BH4" s="77"/>
       <c r="BI4" s="197"/>
-      <c r="BJ4" s="200" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="BK4" s="197" t="n">
-        <v>0.4</v>
+      <c r="BJ4" s="192" t="n">
+        <v>60</v>
+      </c>
+      <c r="BK4" s="193" t="n">
+        <v>40</v>
       </c>
       <c r="BL4" s="192" t="s">
         <v>162</v>
